--- a/docs/nli-report-20260922.xlsx
+++ b/docs/nli-report-20260922.xlsx
@@ -18,11 +18,11 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'אפס שנשמט'!$A$1:$J$45</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'קואורדינטות שגויות'!$A$1:$M$114</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'קואורדינטות שגויות'!$A$1:$M$109</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'034 פגום'!$A$1:$E$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'מזהה ויקינתונים'!$A$1:$J$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'מזהה ויקינתונים'!$A$1:$K$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'כפילות ברשומות'!$A$1:$J$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'בודדות'!$A$1:$G$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'בודדות'!$A$1:$G$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -515,7 +515,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">    קואורדינטות שגויות — 113 שורות — הקואורדינטות ברשומה מצביעות על מקום אחר</t>
+          <t xml:space="preserve">    קואורדינטות שגויות — 108 שורות — הקואורדינטות ברשומה מצביעות על מקום אחר</t>
         </is>
       </c>
     </row>
@@ -529,7 +529,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">    מזהה ויקינתונים — 2 שורות — מזהה ויקינתונים בשדה 024 מצביע על ישות שגויה</t>
+          <t xml:space="preserve">    מזהה ויקינתונים — 8 שורות — מזהה ויקינתונים בשדה 024</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">    בודדות — 3 שורות — תקלות בודדות</t>
+          <t xml:space="preserve">    בודדות — 2 שורות — תקלות בודדות</t>
         </is>
       </c>
     </row>
@@ -2826,7 +2826,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M114"/>
+  <dimension ref="A1:M109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2914,88 +2914,88 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>אוקיאניה</t>
+          <t>טהיילהיים (גרמניה)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Oceania</t>
+          <t>Theilheim (Germany)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>987007543674705171</t>
+          <t>987007507581905171</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-21.00000, 166.00000</t>
+          <t>49.75870, 10.50924</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-18.51020, 139.36710</t>
+          <t>49.94330, 10.14780</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2797.7</v>
+        <v>33.1</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>river/region/range — both points lie on the feature, no real move</t>
+          <t>Wikidata backs Kima's point; NLI's stands alone</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Q538</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Q55643</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
+          <t>Q2416499</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2822902</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007543674705171</t>
+          <t>https://www.nli.org.il/he/authorities/987007507581905171</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>טהיילהיים (גרמניה)</t>
+          <t>גוריי (פולין)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Theilheim (Germany)</t>
+          <t>Goraj (Poland)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>987007507581905171</t>
+          <t>987007522876305171</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>49.75870, 10.50924</t>
+          <t>53.96590, 19.59161</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>49.94330, 10.14780</t>
+          <t>50.71667, 22.65000</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>33.1</v>
+        <v>416.7</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -3004,181 +3004,173 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Q2416499</t>
+          <t>Q1893589</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2822902</t>
+          <t>7532897</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007507581905171</t>
+          <t>https://www.nli.org.il/he/authorities/987007522876305171</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>אטרס-ברג (גרמניה)</t>
+          <t>פודהייל (פולין)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Etters-Berg (Germany)</t>
+          <t>Podhale (Poland)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>987007561549805171</t>
+          <t>987007558385105171</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>51.03333, 11.27972</t>
+          <t>49.47930, 20.02910</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>51.86667, 10.58333</t>
+          <t>50.84401, 20.64039</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>104.5</v>
+        <v>157.9</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Kima is bound to a same-named place elsewhere — a link error, not a move</t>
+          <t>Kima's point disagrees with NLI and with Kima's own Wikidata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Q651583</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Q31547753</t>
-        </is>
-      </c>
+          <t>Q115155</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2928643</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>אלה הם שני מקומות שונים: העיר וההר. אם הכוונה לעיר, הויקידאטה הוא Q651583 והשם: הויקידאטה והקואורדינטות הנוכחיות ב-nli הן לא של etters-berg אלא של ettersburg הישוב. אם הכוונה היא להר, ממליצה לשנות את השם לאטרס-ברג (גרמניה: הר) והויקידאטה הוא  Q31547753</t>
-        </is>
-      </c>
+          <t>8426167</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007561549805171</t>
+          <t>https://www.nli.org.il/he/authorities/987007558385105171</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>גוריי (פולין)</t>
+          <t>אלף האיים (אינדונזיה)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Goraj (Poland)</t>
+          <t>Thousand Islands (Indonesia)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>987007522876305171</t>
+          <t>987007290978605171</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>53.96590, 19.59161</t>
+          <t>1.07895, 117.90961</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>50.71667, 22.65000</t>
+          <t>-5.66290, 106.56830</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>416.7</v>
+        <v>1465.6</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
+          <t>Kima is bound to a same-named place elsewhere — a link error, not a move</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Q1893589</t>
+          <t>Q10107</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>7532897</t>
+          <t>5140907</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007522876305171</t>
+          <t>https://www.nli.org.il/he/authorities/987007290978605171</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>פודהייל (פולין)</t>
+          <t>ביג ת'יקט (טקסס)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Podhale (Poland)</t>
+          <t>Big Thicket (Tex.)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>987007558385105171</t>
+          <t>987007534295705171</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>49.47930, 20.02910</t>
+          <t>31.11323, -98.43754</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>50.84401, 20.64039</t>
+          <t>30.54750, -94.34000</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>157.9</v>
+        <v>396.2</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Kima's point disagrees with NLI and with Kima's own Wikidata</t>
+          <t>Wikidata backs Kima's point; NLI's stands alone</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -3188,54 +3180,54 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Q115155</t>
+          <t>Q34696004</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>8426167</t>
+          <t>4674406</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007558385105171</t>
+          <t>https://www.nli.org.il/he/authorities/987007534295705171</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>אלף האיים (אינדונזיה)</t>
+          <t>הימרה (עיר קדומה)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Thousand Islands (Indonesia)</t>
+          <t>Himera (Extinct city)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>987007290978605171</t>
+          <t>987007561062905171</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.07895, 117.90961</t>
+          <t>37.65940, 14.10460</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-5.66290, 106.56830</t>
+          <t>37.97055, 13.82221</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1465.6</v>
+        <v>42.6</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Kima is bound to a same-named place elsewhere — a link error, not a move</t>
+          <t>Wikidata backs Kima's point; NLI's stands alone</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -3245,50 +3237,46 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Q10107</t>
+          <t>Q1111219</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>5140907</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007290978605171</t>
+          <t>https://www.nli.org.il/he/authorities/987007561062905171</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>נהר רריטן (ניו ג'רזי)</t>
+          <t>הרי וואסאץ' (יוטה ואיידהו)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Raritan River (N.J.)</t>
+          <t>Wasatch Range (Utah and Idaho)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>987007546333605171</t>
+          <t>987007551287205171</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>40.49722, -74.26444</t>
+          <t>39.82139, -111.75972</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>40.62910, -74.88970</t>
+          <t>40.49000, -111.69611</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>54.8</v>
+        <v>74.5</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -3302,54 +3290,50 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Q34709250</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Q749287</t>
-        </is>
-      </c>
+          <t>Q1544388</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>5103129</t>
+          <t>5549209</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007546333605171</t>
+          <t>https://www.nli.org.il/he/authorities/987007551287205171</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ביג ת'יקט (טקסס)</t>
+          <t>מאיר שפיה (ישראל)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Big Thicket (Tex.)</t>
+          <t>Me'ir Shfeya (Israel)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>987007534295705171</t>
+          <t>987007565185505171</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>31.11323, -98.43754</t>
+          <t>32.10197, 34.87391</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>30.54750, -94.34000</t>
+          <t>32.59034, 34.97064</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>396.2</v>
+        <v>55.1</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -3363,64 +3347,60 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Q34696004</t>
+          <t>Q2777355</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>4674406</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007534295705171</t>
+          <t>https://www.nli.org.il/he/authorities/987007565185505171</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>הימרה (עיר קדומה)</t>
+          <t>אתר יפתחאל (ישראל)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Himera (Extinct city)</t>
+          <t>Yiftahel Site (Israel)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>987007561062905171</t>
+          <t>987007549317505171</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>37.65940, 14.10460</t>
+          <t>32.75540, 35.22770</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>37.97055, 13.82221</t>
+          <t>37.92500, 29.12583</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>42.6</v>
+        <v>797.6</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
+          <t>Kima's Wikidata id points at the wrong entity</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Q1111219</t>
+          <t>Q4228288</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
@@ -3428,95 +3408,87 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007561062905171</t>
+          <t>https://www.nli.org.il/he/authorities/987007549317505171</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>הרי וואסאץ' (יוטה ואיידהו)</t>
+          <t>חיילונגג'יאנג (סין)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Wasatch Range (Utah and Idaho)</t>
+          <t>Heilongjiang Sheng (China)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>987007551287205171</t>
+          <t>987012219373405171</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>39.82139, -111.75972</t>
+          <t>48.00000, 128.00000</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>40.49000, -111.69611</t>
+          <t>45.70700, 126.61700</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>74.5</v>
+        <v>275.8</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>river/region/range — both points lie on the feature, no real move</t>
+          <t>Wikidata backs Kima's point; NLI's stands alone</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Q1544388</t>
-        </is>
-      </c>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>5549209</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007551287205171</t>
+          <t>https://www.nli.org.il/he/authorities/987012219373405171</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>מאיר שפיה (ישראל)</t>
+          <t>קאסל (גרמניה)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Me'ir Shfeya (Israel)</t>
+          <t>Kassel (Germany)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>987007565185505171</t>
+          <t>987007564322205171</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>32.10197, 34.87391</t>
+          <t>50.20017, 9.28866</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>32.59034, 34.97064</t>
+          <t>51.31578, 9.49792</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>55.1</v>
+        <v>124.9</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -3530,50 +3502,54 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Q2777355</t>
+          <t>Q2865</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2892518</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007565185505171</t>
+          <t>https://www.nli.org.il/he/authorities/987007564322205171</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>אתר יפתחאל (ישראל)</t>
+          <t>צ'אד, אגם</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Yiftahel Site (Israel)</t>
+          <t>Chad, Lake</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>987007549317505171</t>
+          <t>987007284803205171</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>32.75540, 35.22770</t>
+          <t>13.00000, 14.00000</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>37.92500, 29.12583</t>
+          <t>13.09926, 14.50463</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>797.6</v>
+        <v>55.8</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Kima's Wikidata id points at the wrong entity</t>
+          <t>Wikidata backs Kima's point; NLI's stands alone</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -3583,50 +3559,46 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Q4228288</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Q4228288</t>
-        </is>
-      </c>
+          <t>Q125309</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007549317505171</t>
+          <t>https://www.nli.org.il/he/authorities/987007284803205171</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>חיילונגג'יאנג (סין)</t>
+          <t>נהר סנט מרי'ס (מישיגן ואונטריו)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Heilongjiang Sheng (China)</t>
+          <t>Saint Marys River (Mich. and Ont.)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>987012219373405171</t>
+          <t>987007529708805171</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>48.00000, 128.00000</t>
+          <t>46.50558, -84.61116</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>45.70700, 126.61700</t>
+          <t>45.95835, -83.89723</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>275.8</v>
+        <v>82</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -3635,47 +3607,55 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Q940488</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>4368319</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987012219373405171</t>
+          <t>https://www.nli.org.il/he/authorities/987007529708805171</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>קאסל (גרמניה)</t>
+          <t>פיניקיה</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Kassel (Germany)</t>
+          <t>Phoenicia</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>987007564322205171</t>
+          <t>987007555456905171</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>50.20017, 9.28866</t>
+          <t>42.08140, -74.31310</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>51.31578, 9.49792</t>
+          <t>34.11667, 35.65000</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>124.9</v>
+        <v>8944.299999999999</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -3689,50 +3669,46 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Q2865</t>
+          <t>Q41642</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>2892518</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007564322205171</t>
+          <t>https://www.nli.org.il/he/authorities/987007555456905171</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>צ'אד, אגם</t>
+          <t>איי אפארסה</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Chad, Lake</t>
+          <t>Éparses Islands</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>987007284803205171</t>
+          <t>987007415889605171</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>13.00000, 14.00000</t>
+          <t>-17.04333, 42.74480</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>13.09926, 14.50463</t>
+          <t>-22.34389, 40.36722</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>55.8</v>
+        <v>639.8</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -3746,7 +3722,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Q125309</t>
+          <t>Q190571</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
@@ -3754,38 +3730,38 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007284803205171</t>
+          <t>https://www.nli.org.il/he/authorities/987007415889605171</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>נהר סנט מרי'ס (מישיגן ואונטריו)</t>
+          <t>המישורים הגדולים</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Saint Marys River (Mich. and Ont.)</t>
+          <t>Great Plains</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>987007529708805171</t>
+          <t>987007540907105171</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>46.50558, -84.61116</t>
+          <t>42.00000, -102.00000</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>45.95835, -83.89723</t>
+          <t>40.00000, -100.00000</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>82</v>
+        <v>278.6</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -3799,50 +3775,46 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Q940488</t>
+          <t>Q12707</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>4368319</t>
-        </is>
-      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007529708805171</t>
+          <t>https://www.nli.org.il/he/authorities/987007540907105171</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>פיניקיה</t>
+          <t>מאלמו (שוודיה)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Phoenicia</t>
+          <t>Malmö (Sweden)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>987007555456905171</t>
+          <t>987007552629505171</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>42.08140, -74.31310</t>
+          <t>57.81667, 16.70000</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>34.11667, 35.65000</t>
+          <t>55.59319, 13.02142</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>8944.299999999999</v>
+        <v>333.9</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -3851,51 +3823,51 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Q41642</t>
-        </is>
-      </c>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2692969</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007555456905171</t>
+          <t>https://www.nli.org.il/he/authorities/987007552629505171</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>איי אפארסה</t>
+          <t>מנסטר בלאקווטר (קרי-קורק ווטררפורד, אירלנד)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Éparses Islands</t>
+          <t>Blackwater, River (Kerry-Cork and Waterford, Ireland)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>987007415889605171</t>
+          <t>987007554238205171</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>-17.04333, 42.74480</t>
+          <t>52.19200, -9.24100</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>-22.34389, 40.36722</t>
+          <t>51.94120, -7.83600</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>639.8</v>
+        <v>100</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -3909,7 +3881,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Q190571</t>
+          <t>Q1464482</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
@@ -3917,38 +3889,38 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007415889605171</t>
+          <t>https://www.nli.org.il/he/authorities/987007554238205171</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>המישורים הגדולים</t>
+          <t>אזור במיין (אפגניסטן)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Great Plains</t>
+          <t>Bāmīān Region (Afghanistan)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>987007540907105171</t>
+          <t>987007282291905171</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>42.00000, -102.00000</t>
+          <t>34.69668, 67.27667</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>40.00000, -100.00000</t>
+          <t>34.81667, 67.81667</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>278.6</v>
+        <v>51.1</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -3957,51 +3929,47 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>Q12707</t>
-        </is>
-      </c>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007540907105171</t>
+          <t>https://www.nli.org.il/he/authorities/987007282291905171</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>מאלמו (שוודיה)</t>
+          <t>עין אל-זייתון (ישראל)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Malmö (Sweden)</t>
+          <t>Ein al-Zeitun (Israel)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>987007552629505171</t>
+          <t>987007524670705171</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>57.81667, 16.70000</t>
+          <t>32.23320, 34.94609</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>55.59319, 13.02142</t>
+          <t>32.98723, 35.49155</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>333.9</v>
+        <v>98.2</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -4010,51 +3978,51 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Q5349602</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>2692969</t>
-        </is>
-      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007552629505171</t>
+          <t>https://www.nli.org.il/he/authorities/987007524670705171</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>מנסטר בלאקווטר (קרי-קורק ווטררפורד, אירלנד)</t>
+          <t>ברוק (גרמניה)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Blackwater, River (Kerry-Cork and Waterford, Ireland)</t>
+          <t>Brück (Germany)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>987007554238205171</t>
+          <t>987007507433105171</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>52.19200, -9.24100</t>
+          <t>50.94320, 7.34129</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>51.94120, -7.83600</t>
+          <t>50.48580, 6.97096</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>100</v>
+        <v>57.2</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -4063,51 +4031,55 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Q1464482</t>
+          <t>Q995940</t>
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2943520</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007554238205171</t>
+          <t>https://www.nli.org.il/he/authorities/987007507433105171</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>אזור במיין (אפגניסטן)</t>
+          <t>שט אל-ערב (איראן ועיראק)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Bāmīān Region (Afghanistan)</t>
+          <t>Shatt al-Arab (Iraq and Iran)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>987007282291905171</t>
+          <t>987007536434705171</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>34.69668, 67.27667</t>
+          <t>29.93690, 48.60770</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>34.81667, 67.81667</t>
+          <t>31.00430, 47.44210</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>51.1</v>
+        <v>163</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -4116,100 +4088,116 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Q166966</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>143160</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007282291905171</t>
+          <t>https://www.nli.org.il/he/authorities/987007536434705171</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>עין אל-זייתון (ישראל)</t>
+          <t>אורנצ'יק (טורקיה)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Ein al-Zeitun (Israel)</t>
+          <t>Örencik (Turkey)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>987007524670705171</t>
+          <t>987007583811505171</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>32.23320, 34.94609</t>
+          <t>37.93480, 37.71533</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>32.98723, 35.49155</t>
+          <t>38.48920, 29.89720</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>98.2</v>
+        <v>685.6</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
+          <t>Kima is bound to a same-named place elsewhere — a link error, not a move</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Q5349602</t>
+          <t>Q4821258</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>741074</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>יש הרבה מקומות בשם זה בטורקיה - במקרה הזה מזהה הויקידאטה לא תואם את הקואורדינטות.</t>
+        </is>
+      </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007524670705171</t>
+          <t>https://www.nli.org.il/he/authorities/987007583811505171</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ברוק (גרמניה)</t>
+          <t>אי הפסחא</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Brück (Germany)</t>
+          <t>Easter Island</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>987007507433105171</t>
+          <t>987007567857705171</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>50.94320, 7.34129</t>
+          <t>-66.41667, 98.76667</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>50.48580, 6.97096</t>
+          <t>-27.11944, -109.35472</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>57.2</v>
+        <v>9345.6</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -4218,55 +4206,51 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Q995940</t>
+          <t>Q14452</t>
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>2943520</t>
-        </is>
-      </c>
+      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007507433105171</t>
+          <t>https://www.nli.org.il/he/authorities/987007567857705171</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>שט אל-ערב (איראן ועיראק)</t>
+          <t>אירופה המזרחית</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Shatt al-Arab (Iraq and Iran)</t>
+          <t>Europe, Eastern</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>987007536434705171</t>
+          <t>987007560192505171</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>29.93690, 48.60770</t>
+          <t>50.82308, -1.46568</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>31.00430, 47.44210</t>
+          <t>49.00000, 31.00000</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>163</v>
+        <v>2314.7</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -4280,54 +4264,50 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Q166966</t>
+          <t>Q27468</t>
         </is>
       </c>
       <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>143160</t>
-        </is>
-      </c>
+      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007536434705171</t>
+          <t>https://www.nli.org.il/he/authorities/987007560192505171</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>אורנצ'יק (טורקיה)</t>
+          <t>הרי האלפים הצרפתיים (צרפת)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Örencik (Turkey)</t>
+          <t>Alps, French (France)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>987007583811505171</t>
+          <t>987007294887505171</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>37.93480, 37.71533</t>
+          <t>46.41667, 10.00000</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>38.48920, 29.89720</t>
+          <t>44.80000, 6.50000</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>685.6</v>
+        <v>326.2</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Kima is bound to a same-named place elsewhere — a link error, not a move</t>
+          <t>Wikidata backs Kima's point; NLI's stands alone</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -4335,56 +4315,44 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Q4821258</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>741074</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>יש הרבה מקומות בשם זה בטורקיה - במקרה הזה מזהה הויקידאטה לא תואם את הקואורדינטות.</t>
-        </is>
-      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007583811505171</t>
+          <t>https://www.nli.org.il/he/authorities/987007294887505171</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>אי הפסחא</t>
+          <t>איי טרמיטי (איטליה)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Easter Island</t>
+          <t>Tremiti Islands (Italy)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>987007567857705171</t>
+          <t>987007541762605171</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-66.41667, 98.76667</t>
+          <t>40.11667, 15.50000</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>-27.11944, -109.35472</t>
+          <t>42.11667, 15.50000</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>9345.6</v>
+        <v>222.4</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -4398,46 +4366,50 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Q14452</t>
+          <t>Q51930</t>
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>3165250</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007567857705171</t>
+          <t>https://www.nli.org.il/he/authorities/987007541762605171</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>אירופה המזרחית</t>
+          <t>גרנד בנקס של ניופאונדלנד</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Europe, Eastern</t>
+          <t>Grand Banks of Newfoundland</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>987007560192505171</t>
+          <t>987007536002505171</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>50.82308, -1.46568</t>
+          <t>45.00000, -53.00000</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>49.00000, 31.00000</t>
+          <t>45.23694, -50.98922</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2314.7</v>
+        <v>160</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -4446,51 +4418,47 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Q27468</t>
-        </is>
-      </c>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007560192505171</t>
+          <t>https://www.nli.org.il/he/authorities/987007536002505171</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>באחו סיגורה (ספרד)</t>
+          <t>גלדיבולדו (טורקיה)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Bajo Segura (Spain)</t>
+          <t>Geldibuldu (Turkey)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>987007284646705171</t>
+          <t>987007537927405171</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>38.08333, 0.86667</t>
+          <t>40.18333, 32.83333</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>38.06693, -0.84042</t>
+          <t>37.72807, 38.86933</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>149.4</v>
+        <v>588.8</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -4499,55 +4467,55 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>Q972305</t>
-        </is>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Q4831991</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2521395</t>
+          <t>312116</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007284646705171</t>
+          <t>https://www.nli.org.il/he/authorities/987007537927405171</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>הרי האלפים הצרפתיים (צרפת)</t>
+          <t>גוס איילנד (שיקגו, אילינוי)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Alps, French (France)</t>
+          <t>Goose Island (Chicago, Ill.)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>987007294887505171</t>
+          <t>987007539410905171</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>46.41667, 10.00000</t>
+          <t>37.12556, -89.40306</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>44.80000, 6.50000</t>
+          <t>41.90392, -87.65394</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>326.2</v>
+        <v>552.1</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -4559,44 +4527,48 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Q5584067</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007294887505171</t>
+          <t>https://www.nli.org.il/he/authorities/987007539410905171</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>איי טרמיטי (איטליה)</t>
+          <t>קמלדולי (איטליה)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Tremiti Islands (Italy)</t>
+          <t>Camaldoli (Italy)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>987007541762605171</t>
+          <t>987007550230005171</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>40.11667, 15.50000</t>
+          <t>40.85000, 14.20000</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>42.11667, 15.50000</t>
+          <t>44.42031, 8.98444</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>222.4</v>
+        <v>582.6</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -4610,99 +4582,103 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Q51930</t>
+          <t>Q18456541</t>
         </is>
       </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>3165250</t>
+          <t>8953134</t>
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007541762605171</t>
+          <t>https://www.nli.org.il/he/authorities/987007550230005171</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>גרנד בנקס של ניופאונדלנד</t>
+          <t>האבלוי (צרפת)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Grand Banks of Newfoundland</t>
+          <t>Haveluy (France)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>987007536002505171</t>
+          <t>987007535425005171</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>45.00000, -53.00000</t>
+          <t>21.00000, 3.40000</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>45.23694, -50.98922</t>
+          <t>50.35289, 3.40389</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>160</v>
+        <v>3263.9</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
+          <t>no Wikidata entity to arbitrate with</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>3013637</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007536002505171</t>
+          <t>https://www.nli.org.il/he/authorities/987007535425005171</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>גלדיבולדו (טורקיה)</t>
+          <t>יוכן (גרמניה)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Geldibuldu (Turkey)</t>
+          <t>Jüchen (Germany)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>987007537927405171</t>
+          <t>987007489333905171</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>40.18333, 32.83333</t>
+          <t>51.50000, 6.50000</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>37.72807, 38.86933</t>
+          <t>51.10111, 6.50167</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>588.8</v>
+        <v>44.4</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -4716,50 +4692,50 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Q4831991</t>
+          <t>Q255416</t>
         </is>
       </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>312116</t>
+          <t>6291043</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007537927405171</t>
+          <t>https://www.nli.org.il/he/authorities/987007489333905171</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>גוס איילנד (שיקגו, אילינוי)</t>
+          <t>מיטשלוויל (קרולינה הדרומית)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Goose Island (Chicago, Ill.)</t>
+          <t>Mitchellville (S.C.)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>987007539410905171</t>
+          <t>987007480256305171</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>37.12556, -89.40306</t>
+          <t>32.46167, -80.99222</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>41.90392, -87.65394</t>
+          <t>41.66722, -93.36028</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>552.1</v>
+        <v>1497.8</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -4768,12 +4744,12 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Q5584067</t>
+          <t>Q1914731</t>
         </is>
       </c>
       <c r="J35" t="inlineStr"/>
@@ -4781,38 +4757,38 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007539410905171</t>
+          <t>https://www.nli.org.il/he/authorities/987007480256305171</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>קמלדולי (איטליה)</t>
+          <t>תל סאוואן (עיראק)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Camaldoli (Italy)</t>
+          <t>Sawwan, Tall (Iraq)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>987007550230005171</t>
+          <t>987007549454405171</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>40.85000, 14.20000</t>
+          <t>36.21222, 42.64972</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>44.42031, 8.98444</t>
+          <t>34.11670, 43.90000</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>582.6</v>
+        <v>259.2</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -4821,165 +4797,153 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>Q18456541</t>
-        </is>
-      </c>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>8953134</t>
-        </is>
-      </c>
+      <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007550230005171</t>
+          <t>https://www.nli.org.il/he/authorities/987007549454405171</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>האבלוי (צרפת)</t>
+          <t>באיו לאפורש (לואיזיאנה)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Haveluy (France)</t>
+          <t>Lafourche, Bayou (La.)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>987007535425005171</t>
+          <t>987007543967105171</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>21.00000, 3.40000</t>
+          <t>32.12194, -91.96806</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>50.35289, 3.40389</t>
+          <t>30.11164, -90.99372</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>3263.9</v>
+        <v>242</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>no Wikidata entity to arbitrate with</t>
+          <t>Wikidata backs Kima's point; NLI's stands alone</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Q2892300</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>3013637</t>
-        </is>
-      </c>
+      <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007535425005171</t>
+          <t>https://www.nli.org.il/he/authorities/987007543967105171</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>יוכן (גרמניה)</t>
+          <t>מפרצון המילטון (ניופאונדלנד ולברדור)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Jüchen (Germany)</t>
+          <t>Hamilton Inlet (N.L.)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>987007489333905171</t>
+          <t>987007537472705171</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>51.50000, 6.50000</t>
+          <t>54.00000, -57.49806</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>51.10111, 6.50167</t>
+          <t>54.30771, -57.68097</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>44.4</v>
+        <v>36.2</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
+          <t>no Wikidata entity to arbitrate with</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>Q255416</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>6291043</t>
+          <t>5969825</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007489333905171</t>
+          <t>https://www.nli.org.il/he/authorities/987007537472705171</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>מיטשלוויל (קרולינה הדרומית)</t>
+          <t>אשנאו (היילברון, גרמניה)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Mitchellville (S.C.)</t>
+          <t>Eschenau (Heilbronn, Germany)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>987007480256305171</t>
+          <t>987007550227305171</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>32.46167, -80.99222</t>
+          <t>49.13333, 9.40000</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>41.66722, -93.36028</t>
+          <t>49.57428, 11.19847</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1497.8</v>
+        <v>139.2</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -4993,7 +4957,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Q1914731</t>
+          <t>Q62080922</t>
         </is>
       </c>
       <c r="J39" t="inlineStr"/>
@@ -5001,38 +4965,38 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007480256305171</t>
+          <t>https://www.nli.org.il/he/authorities/987007550227305171</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>תל סאוואן (עיראק)</t>
+          <t>וייטנאם הדרומית</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Sawwan, Tall (Iraq)</t>
+          <t>Vietnam, Southern</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>987007549454405171</t>
+          <t>987007554119405171</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>36.21222, 42.64972</t>
+          <t>11.00000, 107.00000</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>34.11670, 43.90000</t>
+          <t>21.46667, 103.06667</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>259.2</v>
+        <v>1237</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -5050,38 +5014,38 @@
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007549454405171</t>
+          <t>https://www.nli.org.il/he/authorities/987007554119405171</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>באיו לאפורש (לואיזיאנה)</t>
+          <t>נהר סלמון (איידהו)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Lafourche, Bayou (La.)</t>
+          <t>Salmon River (Idaho)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>987007543967105171</t>
+          <t>987007553584105171</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>32.12194, -91.96806</t>
+          <t>45.85639, -116.79361</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>30.11164, -90.99372</t>
+          <t>44.57490, -114.49600</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>242</v>
+        <v>229.5</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -5090,104 +5054,100 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>Q2892300</t>
-        </is>
-      </c>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>6139605</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007543967105171</t>
+          <t>https://www.nli.org.il/he/authorities/987007553584105171</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>מפרצון המילטון (ניופאונדלנד ולברדור)</t>
+          <t>אתר בני חסן (מצרים)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Hamilton Inlet (N.L.)</t>
+          <t>Banī Ḥasan Site (Egypt)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>987007537472705171</t>
+          <t>987007551513105171</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>54.00000, -57.49806</t>
+          <t>30.90000, 31.68333</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>54.30771, -57.68097</t>
+          <t>27.93139, 30.87528</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>36.2</v>
+        <v>339.2</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>no Wikidata entity to arbitrate with</t>
+          <t>Wikidata backs Kima's point; NLI's stands alone</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>5969825</t>
-        </is>
-      </c>
+      <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007537472705171</t>
+          <t>https://www.nli.org.il/he/authorities/987007551513105171</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>אשנאו (היילברון, גרמניה)</t>
+          <t>נהר מינו (ספרד ופורטוגל)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Eschenau (Heilbronn, Germany)</t>
+          <t>Miño River (Spain and Portugal)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>987007550227305171</t>
+          <t>987007529996605171</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>49.13333, 9.40000</t>
+          <t>41.86667, -8.85000</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>49.57428, 11.19847</t>
+          <t>43.21139, -7.28111</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>139.2</v>
+        <v>197.2</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -5201,7 +5161,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Q62080922</t>
+          <t>Q14554</t>
         </is>
       </c>
       <c r="J43" t="inlineStr"/>
@@ -5209,38 +5169,38 @@
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007550227305171</t>
+          <t>https://www.nli.org.il/he/authorities/987007529996605171</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>וייטנאם הדרומית</t>
+          <t>קאדור (איטליה)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Vietnam, Southern</t>
+          <t>Cadore (Italy)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>987007554119405171</t>
+          <t>987007566295205171</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>11.00000, 107.00000</t>
+          <t>46.50917, 12.35722</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>21.46667, 103.06667</t>
+          <t>45.72222, 11.65762</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1237</v>
+        <v>102.8</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -5252,44 +5212,48 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Q18505996</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007554119405171</t>
+          <t>https://www.nli.org.il/he/authorities/987007566295205171</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>נהר סלמון (איידהו)</t>
+          <t>הויבך (באדן-וירטמברג, גרמניה)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Salmon River (Idaho)</t>
+          <t>Heubach (Baden-Württemberg, Germany)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>987007553584105171</t>
+          <t>987007564639705171</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>45.85639, -116.79361</t>
+          <t>51.80000, 7.25000</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>44.57490, -114.49600</t>
+          <t>48.78333, 9.93333</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>229.5</v>
+        <v>385.8</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -5298,51 +5262,55 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Q326437</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
-          <t>6139605</t>
+          <t>2905154</t>
         </is>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007553584105171</t>
+          <t>https://www.nli.org.il/he/authorities/987007564639705171</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>אתר בני חסן (מצרים)</t>
+          <t>היספניולה</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Banī Ḥasan Site (Egypt)</t>
+          <t>Hispaniola</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>987007551513105171</t>
+          <t>987007560553605171</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>30.90000, 31.68333</t>
+          <t>-62.66361, -60.38139</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>27.93139, 30.87528</t>
+          <t>19.00000, -71.00000</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>339.2</v>
+        <v>9128.4</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -5351,47 +5319,51 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Q25277</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007551513105171</t>
+          <t>https://www.nli.org.il/he/authorities/987007560553605171</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>נהר מינו (ספרד ופורטוגל)</t>
+          <t>חצי האי מלוויל (נונאווט)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Miño River (Spain and Portugal)</t>
+          <t>Melville Peninsula (Nunavut)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>987007529996605171</t>
+          <t>987007566381305171</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>41.86667, -8.85000</t>
+          <t>67.50000, -84.00000</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>43.21139, -7.28111</t>
+          <t>68.00097, -83.99891</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>197.2</v>
+        <v>55.7</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -5405,46 +5377,50 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Q14554</t>
+          <t>Q1352266</t>
         </is>
       </c>
       <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>6071994</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007529996605171</t>
+          <t>https://www.nli.org.il/he/authorities/987007566381305171</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>קאדור (איטליה)</t>
+          <t>בניאס (עיר קדומה) (ישראל)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Cadore (Italy)</t>
+          <t>Banias (Extinct city) (Israel)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>987007566295205171</t>
+          <t>987007554831505171</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>46.50917, 12.35722</t>
+          <t>35.18222, 35.94028</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>45.72222, 11.65762</t>
+          <t>33.24861, 35.69444</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>102.8</v>
+        <v>216.2</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -5453,12 +5429,12 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Q18505996</t>
+          <t>Q606295</t>
         </is>
       </c>
       <c r="J48" t="inlineStr"/>
@@ -5466,38 +5442,38 @@
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007566295205171</t>
+          <t>https://www.nli.org.il/he/authorities/987007554831505171</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>הויבך (באדן-וירטמברג, גרמניה)</t>
+          <t>בוקובינה (רומניה ואוקראינה)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Heubach (Baden-Württemberg, Germany)</t>
+          <t>Bukovina (Romania and Ukraine)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>987007564639705171</t>
+          <t>987007534359505171</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>51.80000, 7.25000</t>
+          <t>47.77670, 22.87199</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>48.78333, 9.93333</t>
+          <t>48.00000, 26.00000</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>385.8</v>
+        <v>234.5</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -5511,50 +5487,50 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Q326437</t>
+          <t>Q105206</t>
         </is>
       </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2905154</t>
+          <t>571096</t>
         </is>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007564639705171</t>
+          <t>https://www.nli.org.il/he/authorities/987007534359505171</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>היספניולה</t>
+          <t>בירוביג'אן (רוסיה)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Hispaniola</t>
+          <t>Birobidzhan (Russia)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>987007560553605171</t>
+          <t>987007554968405171</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>-62.66361, -60.38139</t>
+          <t>49.80000, 132.95000</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>19.00000, -71.00000</t>
+          <t>48.78333, 132.93333</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>9128.4</v>
+        <v>113.1</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -5568,46 +5544,50 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Q25277</t>
+          <t>Q7769</t>
         </is>
       </c>
       <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>2026643</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007560553605171</t>
+          <t>https://www.nli.org.il/he/authorities/987007554968405171</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>חצי האי מלוויל (נונאווט)</t>
+          <t>מונטפיאסקונה (איטליה)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Melville Peninsula (Nunavut)</t>
+          <t>Montefiascone (Italy)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>987007566381305171</t>
+          <t>987007564957105171</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>67.50000, -84.00000</t>
+          <t>42.53957, 12.51957</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>68.00097, -83.99891</t>
+          <t>42.53333, 12.03333</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>55.7</v>
+        <v>39.8</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -5621,64 +5601,64 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Q1352266</t>
+          <t>Q176142</t>
         </is>
       </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>6071994</t>
+          <t>3172931</t>
         </is>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007566381305171</t>
+          <t>https://www.nli.org.il/he/authorities/987007564957105171</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>בניאס (עיר קדומה) (ישראל)</t>
+          <t>קיליקיה</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Banias (Extinct city) (Israel)</t>
+          <t>Cilicia</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>987007554831505171</t>
+          <t>987007562363005171</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>35.18222, 35.94028</t>
+          <t>-44.36667, 168.51667</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>33.24861, 35.69444</t>
+          <t>36.98500, 35.12000</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>216.2</v>
+        <v>16055.5</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
+          <t>Kima is bound to a same-named place elsewhere — a link error, not a move</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Q606295</t>
+          <t>Q31651596</t>
         </is>
       </c>
       <c r="J52" t="inlineStr"/>
@@ -5686,38 +5666,38 @@
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007554831505171</t>
+          <t>https://www.nli.org.il/he/authorities/987007562363005171</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>בוקובינה (רומניה ואוקראינה)</t>
+          <t>גליפולי (איטליה)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Bukovina (Romania and Ukraine)</t>
+          <t>Gallipoli (Italy)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>987007534359505171</t>
+          <t>987007562365105171</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>47.77670, 22.87199</t>
+          <t>40.54587, 18.06820</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>48.00000, 26.00000</t>
+          <t>40.05556, 17.99167</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>234.5</v>
+        <v>54.9</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -5731,50 +5711,50 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Q105206</t>
+          <t>Q52143</t>
         </is>
       </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
-          <t>571096</t>
+          <t>11886622</t>
         </is>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007534359505171</t>
+          <t>https://www.nli.org.il/he/authorities/987007562365105171</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>בירוביג'אן (רוסיה)</t>
+          <t>איי מריאנה</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Birobidzhan (Russia)</t>
+          <t>Mariana Islands</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>987007554968405171</t>
+          <t>987007562324405171</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>49.80000, 132.95000</t>
+          <t>16.13333, 145.75000</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>48.78333, 132.93333</t>
+          <t>16.70000, 145.78000</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>113.1</v>
+        <v>63.1</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -5788,50 +5768,46 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Q7769</t>
+          <t>Q153732</t>
         </is>
       </c>
       <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>2026643</t>
-        </is>
-      </c>
+      <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007554968405171</t>
+          <t>https://www.nli.org.il/he/authorities/987007562324405171</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>מונטפיאסקונה (איטליה)</t>
+          <t>וילוויז' (לגניצה, פולין)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Montefiascone (Italy)</t>
+          <t>Wielowieś (Legnica, Poland)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>987007564957105171</t>
+          <t>987007560013405171</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>42.53957, 12.51957</t>
+          <t>51.33598, 16.36796</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>42.53333, 12.03333</t>
+          <t>51.76670, 17.35000</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>39.8</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -5845,64 +5821,60 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Q176142</t>
+          <t>Q7999090</t>
         </is>
       </c>
       <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>3172931</t>
-        </is>
-      </c>
+      <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007564957105171</t>
+          <t>https://www.nli.org.il/he/authorities/987007560013405171</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>קיליקיה</t>
+          <t>בורבק (אסן, גרמניה)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Cilicia</t>
+          <t>Borbeck (Essen, Germany)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>987007562363005171</t>
+          <t>987007564629705171</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>-44.36667, 168.51667</t>
+          <t>51.48333, 6.95000</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>36.98500, 35.12000</t>
+          <t>53.20583, 8.14806</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>16055.5</v>
+        <v>208.1</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Kima is bound to a same-named place elsewhere — a link error, not a move</t>
+          <t>Wikidata backs Kima's point; NLI's stands alone</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Q31651596</t>
+          <t>Q15107863</t>
         </is>
       </c>
       <c r="J56" t="inlineStr"/>
@@ -5910,38 +5882,38 @@
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007562363005171</t>
+          <t>https://www.nli.org.il/he/authorities/987007564629705171</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>גליפולי (איטליה)</t>
+          <t>קודי (אינדונזיה)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Gallipoli (Italy)</t>
+          <t>Kodi (Indonesia)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>987007562365105171</t>
+          <t>987007564905705171</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>40.54587, 18.06820</t>
+          <t>-33.00000, 118.98333</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>40.05556, 17.99167</t>
+          <t>-9.59270, 118.98559</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>54.9</v>
+        <v>2602.8</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -5955,103 +5927,103 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Q52143</t>
+          <t>Q2451145</t>
         </is>
       </c>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
-          <t>11886622</t>
+          <t>627127</t>
         </is>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007562365105171</t>
+          <t>https://www.nli.org.il/he/authorities/987007564905705171</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>איי מריאנה</t>
+          <t>אוברשופהיים (גרמניה)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Mariana Islands</t>
+          <t>Oberschopfheim (Germany)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>987007562324405171</t>
+          <t>987007567706405171</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>16.13333, 145.75000</t>
+          <t>26.00000, 7.90000</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>16.70000, 145.78000</t>
+          <t>48.39675, 7.90280</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>63.1</v>
+        <v>2490.4</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
+          <t>Kima is bound to a same-named place elsewhere — a link error, not a move</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>Q153732</t>
-        </is>
-      </c>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>2859099</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007562324405171</t>
+          <t>https://www.nli.org.il/he/authorities/987007567706405171</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>וילוויז' (לגניצה, פולין)</t>
+          <t>גרמפיאן (סקוטלנד)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Wielowieś (Legnica, Poland)</t>
+          <t>Grampian (Scotland)</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>987007560013405171</t>
+          <t>987007561908705171</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>51.33598, 16.36796</t>
+          <t>57.26667, 3.16667</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>51.76670, 17.35000</t>
+          <t>57.26667, -3.16667</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>83.09999999999999</v>
+        <v>380.7</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -6060,51 +6032,51 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>Q7999090</t>
-        </is>
-      </c>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>2648228</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007560013405171</t>
+          <t>https://www.nli.org.il/he/authorities/987007561908705171</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>בורבק (אסן, גרמניה)</t>
+          <t>יונאן שנג (סין)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Borbeck (Essen, Germany)</t>
+          <t>Yunnan Sheng (China)</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>987007564629705171</t>
+          <t>987007564562205171</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>51.48333, 6.95000</t>
+          <t>31.40000, 121.40000</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>53.20583, 8.14806</t>
+          <t>25.04944, 102.70889</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>208.1</v>
+        <v>1959.3</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -6118,7 +6090,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Q15107863</t>
+          <t>Q43194</t>
         </is>
       </c>
       <c r="J60" t="inlineStr"/>
@@ -6126,38 +6098,38 @@
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007564629705171</t>
+          <t>https://www.nli.org.il/he/authorities/987007564562205171</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>קודי (אינדונזיה)</t>
+          <t>בלמונטה קלברו (איטליה)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Kodi (Indonesia)</t>
+          <t>Belmonte Calabro (Italy)</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>987007564905705171</t>
+          <t>987007564560905171</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>-33.00000, 118.98333</t>
+          <t>39.16398, 16.82145</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>-9.59270, 118.98559</t>
+          <t>39.16667, 16.08333</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>2602.8</v>
+        <v>63.6</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -6171,50 +6143,50 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Q2451145</t>
+          <t>Q53835</t>
         </is>
       </c>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
-          <t>627127</t>
+          <t>2525574</t>
         </is>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007564905705171</t>
+          <t>https://www.nli.org.il/he/authorities/987007564560905171</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>אוברשופהיים (גרמניה)</t>
+          <t>ווטרלו (אונטריו)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Oberschopfheim (Germany)</t>
+          <t>Waterloo (Ont.)</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>987007567706405171</t>
+          <t>987007564605705171</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>26.00000, 7.90000</t>
+          <t>43.47970, -80.54110</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>48.39675, 7.90280</t>
+          <t>50.71469, 4.39910</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>2490.4</v>
+        <v>6119.3</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -6230,44 +6202,44 @@
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2859099</t>
+          <t>2783985</t>
         </is>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007567706405171</t>
+          <t>https://www.nli.org.il/he/authorities/987007564605705171</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>גרמפיאן (סקוטלנד)</t>
+          <t>סטז'יז'וב (מחוז התת-קרפטיים, פולין)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Grampian (Scotland)</t>
+          <t>Strzyżów (Województwo Podkarpackie, Poland)</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>987007561908705171</t>
+          <t>987007564939605171</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>57.26667, 3.16667</t>
+          <t>50.35766, 22.41229</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>57.26667, -3.16667</t>
+          <t>49.87083, 21.79111</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>380.7</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -6276,51 +6248,55 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Q835423</t>
+        </is>
+      </c>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2648228</t>
+          <t>757957</t>
         </is>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007561908705171</t>
+          <t>https://www.nli.org.il/he/authorities/987007564939605171</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>יונאן שנג (סין)</t>
+          <t>בוליבר (קולומביה : מחוז)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Yunnan Sheng (China)</t>
+          <t>Bolívar (Colombia : Department)</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>987007564562205171</t>
+          <t>987007564339005171</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>31.40000, 121.40000</t>
+          <t>-17.96667, -66.53333</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>25.04944, 102.70889</t>
+          <t>8.88333, -74.31667</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>1959.3</v>
+        <v>3105.5</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -6334,7 +6310,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Q43194</t>
+          <t>Q230597</t>
         </is>
       </c>
       <c r="J64" t="inlineStr"/>
@@ -6342,148 +6318,156 @@
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007564562205171</t>
+          <t>https://www.nli.org.il/he/authorities/987007564339005171</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>בלמונטה קלברו (איטליה)</t>
+          <t>ורז'ם גרנדה (ברזיל)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Belmonte Calabro (Italy)</t>
+          <t>Vargem Grande (Brazil)</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>987007564560905171</t>
+          <t>987007564873205171</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>39.16398, 16.82145</t>
+          <t>-8.83333, -42.50000</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>39.16667, 16.08333</t>
+          <t>-21.90139, -43.18167</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>63.6</v>
+        <v>1454.9</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
+          <t>Wikidata agrees with neither point</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Q53835</t>
+          <t>Q22014977</t>
         </is>
       </c>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2525574</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr"/>
+          <t>3476725</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>-3.54306, -43.91583 הן הקואורדינטות הנכון (ראו ויקידאטה)</t>
+        </is>
+      </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007564560905171</t>
+          <t>https://www.nli.org.il/he/authorities/987007564873205171</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ווטרלו (אונטריו)</t>
+          <t>סולון (צרפת)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Waterloo (Ont.)</t>
+          <t>Sologne (France)</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>987007564605705171</t>
+          <t>987007567019805171</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>43.47970, -80.54110</t>
+          <t>47.83333, 3.00000</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>50.71469, 4.39910</t>
+          <t>47.83333, 2.00000</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>6119.3</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Kima is bound to a same-named place elsewhere — a link error, not a move</t>
+          <t>no Wikidata entity to arbitrate with</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2783985</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr"/>
+          <t>2974334</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>הסולן הוא מדרום ללואר</t>
+        </is>
+      </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007564605705171</t>
+          <t>https://www.nli.org.il/he/authorities/987007567019805171</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>סטז'יז'וב (מחוז התת-קרפטיים, פולין)</t>
+          <t>שופרונקיהידה (הונגריה)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Strzyżów (Województwo Podkarpackie, Poland)</t>
+          <t>Sopronkőhida (Hungary)</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>987007564939605171</t>
+          <t>987007562299405171</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>50.35766, 22.41229</t>
+          <t>47.73333, 18.63333</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>49.87083, 21.79111</t>
+          <t>47.72317, 16.62178</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>69.90000000000001</v>
+        <v>150.5</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -6497,50 +6481,50 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Q835423</t>
+          <t>Q718321</t>
         </is>
       </c>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr">
         <is>
-          <t>757957</t>
+          <t>3049576</t>
         </is>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007564939605171</t>
+          <t>https://www.nli.org.il/he/authorities/987007562299405171</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>בוליבר (קולומביה : מחוז)</t>
+          <t>שבווה (תימן : פרובינציה)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Bolívar (Colombia : Department)</t>
+          <t>Shabwah (Yemen : Province)</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>987007564339005171</t>
+          <t>987007567130205171</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>-17.96667, -66.53333</t>
+          <t>15.00000, 47.00000</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>8.88333, -74.31667</t>
+          <t>16.15306, 43.18667</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>3105.5</v>
+        <v>428.1</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -6554,7 +6538,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Q230597</t>
+          <t>Q20308083</t>
         </is>
       </c>
       <c r="J68" t="inlineStr"/>
@@ -6562,166 +6546,158 @@
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007564339005171</t>
+          <t>https://www.nli.org.il/he/authorities/987007567130205171</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>סולון (צרפת)</t>
+          <t>אמפלאקיה (יוון)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Sologne (France)</t>
+          <t>Ampelakia (Greece)</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>987007567019805171</t>
+          <t>987007566950505171</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>47.83333, 3.00000</t>
+          <t>39.85000, 22.55000</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>47.83333, 2.00000</t>
+          <t>40.93061, 25.36914</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>74.59999999999999</v>
+        <v>267.3</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>no Wikidata entity to arbitrate with</t>
+          <t>Wikidata backs Kima's point; NLI's stands alone</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Q21405391</t>
+        </is>
+      </c>
       <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>2974334</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>הסולן הוא מדרום ללואר</t>
-        </is>
-      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007567019805171</t>
+          <t>https://www.nli.org.il/he/authorities/987007566950505171</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>שופרונקיהידה (הונגריה)</t>
+          <t>ליקיה</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Sopronkőhida (Hungary)</t>
+          <t>Lycia</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>987007562299405171</t>
+          <t>987007562204705171</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>47.73333, 18.63333</t>
+          <t>35.05000, 28.75000</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>47.72317, 16.62178</t>
+          <t>36.73333, 29.90000</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>150.5</v>
+        <v>213.9</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
+          <t>Kima is bound to a same-named place elsewhere — a link error, not a move</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Q718321</t>
+          <t>Q3268401</t>
         </is>
       </c>
       <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>3049576</t>
-        </is>
-      </c>
+      <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007562299405171</t>
+          <t>https://www.nli.org.il/he/authorities/987007562204705171</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>שבווה (תימן : פרובינציה)</t>
+          <t>חסקוי (איסטנבול, טורקיה)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Shabwah (Yemen : Province)</t>
+          <t>Hasköy (Istanbul, Turkey)</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>987007567130205171</t>
+          <t>987007583688105171</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>15.00000, 47.00000</t>
+          <t>41.38263, 28.95166</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>16.15306, 43.18667</t>
+          <t>41.03972, 28.94972</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>428.1</v>
+        <v>38.1</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
+          <t>Kima is bound to a same-named place elsewhere — a link error, not a move</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Q20308083</t>
+          <t>Q1011290</t>
         </is>
       </c>
       <c r="J71" t="inlineStr"/>
@@ -6729,95 +6705,91 @@
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007567130205171</t>
+          <t>https://www.nli.org.il/he/authorities/987007583688105171</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>גרינוולד (פולין)</t>
+          <t>מוט (מרסין אילי, טורקיה)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Grunwald (Poland)</t>
+          <t>Mut (Mersin İli, Turkey)</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>987007564769205171</t>
+          <t>987007560132205171</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>48.04831, 11.53169</t>
+          <t>36.65000, 32.45000</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>53.48583, 20.09194</t>
+          <t>36.64583, 33.43750</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>852.1</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Kima is bound to a same-named place elsewhere — a link error, not a move</t>
+          <t>Wikidata backs Kima's point; NLI's stands alone</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Q220090</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>Q1025864</t>
-        </is>
-      </c>
+          <t>Q94637</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007564769205171</t>
+          <t>https://www.nli.org.il/he/authorities/987007560132205171</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>אמפלאקיה (יוון)</t>
+          <t>סרוצק (ורשה, פולין)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Ampelakia (Greece)</t>
+          <t>Serock (Warsaw, Poland)</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>987007566950505171</t>
+          <t>987007560004305171</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>39.85000, 22.55000</t>
+          <t>52.24667, 21.54659</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>40.93061, 25.36914</t>
+          <t>52.51306, 21.06944</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>267.3</v>
+        <v>43.9</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -6831,103 +6803,107 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Q21405391</t>
+          <t>Q569838</t>
         </is>
       </c>
       <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>759470</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007566950505171</t>
+          <t>https://www.nli.org.il/he/authorities/987007560004305171</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ליקיה</t>
+          <t>פטרובקה (רוסיה : רפובליקה)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Lycia</t>
+          <t>Petrovka (R.S.F.S.R.)</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>987007562204705171</t>
+          <t>987007562383005171</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>35.05000, 28.75000</t>
+          <t>60.83333, 28.83333</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>36.73333, 29.90000</t>
+          <t>57.19083, 83.92639</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>213.9</v>
+        <v>3085.2</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Kima is bound to a same-named place elsewhere — a link error, not a move</t>
+          <t>no Wikidata entity to arbitrate with</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>Q3268401</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>1495080</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007562204705171</t>
+          <t>https://www.nli.org.il/he/authorities/987007562383005171</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>חסקוי (איסטנבול, טורקיה)</t>
+          <t>פרובינציה מזרח בריטניה החדש (פפואה גינאה החדשה)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Hasköy (Istanbul, Turkey)</t>
+          <t>East New Britain Province (Papua New Guinea)</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>987007583688105171</t>
+          <t>987007567509405171</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>41.38263, 28.95166</t>
+          <t>-6.50000, 152.50000</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>41.03972, 28.94972</t>
+          <t>-4.61283, 151.88775</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>38.1</v>
+        <v>220.5</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Kima is bound to a same-named place elsewhere — a link error, not a move</t>
+          <t>Wikidata backs Kima's point; NLI's stands alone</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -6935,48 +6911,48 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>Q1011290</t>
-        </is>
-      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>2097853</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007583688105171</t>
+          <t>https://www.nli.org.il/he/authorities/987007567509405171</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>מוט (מרסין אילי, טורקיה)</t>
+          <t>פארצ'ב (לובלין, פולין)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Mut (Mersin İli, Turkey)</t>
+          <t>Parczew (Lublin, Poland)</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>987007560132205171</t>
+          <t>987007567513705171</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>36.65000, 32.45000</t>
+          <t>52.30738, 23.43160</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>36.64583, 33.43750</t>
+          <t>51.63333, 22.86667</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>88.09999999999999</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -6990,7 +6966,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Q94637</t>
+          <t>Q2343396</t>
         </is>
       </c>
       <c r="J76" t="inlineStr"/>
@@ -6998,38 +6974,38 @@
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007560132205171</t>
+          <t>https://www.nli.org.il/he/authorities/987007567513705171</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>סרוצק (ורשה, פולין)</t>
+          <t>הורודלה (פולין)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Serock (Warsaw, Poland)</t>
+          <t>Horodło (Poland)</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>987007560004305171</t>
+          <t>987007559990305171</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>52.24667, 21.54659</t>
+          <t>50.89437, 24.73120</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>52.51306, 21.06944</t>
+          <t>50.88333, 24.03333</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>43.9</v>
+        <v>49</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -7043,103 +7019,103 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Q569838</t>
+          <t>Q934815</t>
         </is>
       </c>
       <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>759470</t>
-        </is>
-      </c>
+      <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007560004305171</t>
+          <t>https://www.nli.org.il/he/authorities/987007559990305171</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>פטרובקה (רוסיה : רפובליקה)</t>
+          <t>בכר (אלג'יריה)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Petrovka (R.S.F.S.R.)</t>
+          <t>Béchar (Algeria)</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>987007562383005171</t>
+          <t>987007567374905171</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>60.83333, 28.83333</t>
+          <t>31.81499, -1.87823</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>57.19083, 83.92639</t>
+          <t>31.63333, -2.20000</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>3085.2</v>
+        <v>36.5</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>no Wikidata entity to arbitrate with</t>
+          <t>Wikidata backs Kima's point; NLI's stands alone</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Q638704</t>
+        </is>
+      </c>
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr">
         <is>
-          <t>1495080</t>
+          <t>6296382</t>
         </is>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007562383005171</t>
+          <t>https://www.nli.org.il/he/authorities/987007567374905171</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>פרובינציה מזרח בריטניה החדש (פפואה גינאה החדשה)</t>
+          <t>ארביל (עיראק)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>East New Britain Province (Papua New Guinea)</t>
+          <t>Erbil (Iraq)</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>987007567509405171</t>
+          <t>987007564435605171</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>-6.50000, 152.50000</t>
+          <t>36.36908, 44.55924</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>-4.61283, 151.88775</t>
+          <t>36.19111, 44.00944</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>220.5</v>
+        <v>53.1</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -7148,51 +7124,51 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Q132754</t>
+        </is>
+      </c>
       <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>2097853</t>
-        </is>
-      </c>
+      <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007567509405171</t>
+          <t>https://www.nli.org.il/he/authorities/987007564435605171</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>פארצ'ב (לובלין, פולין)</t>
+          <t>חנטשין (מחוז שוויינטוקז'יסקיה, פולין)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Parczew (Lublin, Poland)</t>
+          <t>Chęciny (Województwo Świętokrzyskie, Poland)</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>987007567513705171</t>
+          <t>987007564539905171</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>52.30738, 23.43160</t>
+          <t>50.81128, 20.46710</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>51.63333, 22.86667</t>
+          <t>51.86833, 21.74556</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>84.40000000000001</v>
+        <v>147.3</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -7206,7 +7182,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Q2343396</t>
+          <t>Q928099</t>
         </is>
       </c>
       <c r="J80" t="inlineStr"/>
@@ -7214,38 +7190,38 @@
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007567513705171</t>
+          <t>https://www.nli.org.il/he/authorities/987007564539905171</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>הורודלה (פולין)</t>
+          <t>טרנקוזו (ברזיל)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Horodło (Poland)</t>
+          <t>Trancoso (Brazil)</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>987007559990305171</t>
+          <t>987007567226805171</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>50.89437, 24.73120</t>
+          <t>40.78330, -7.35000</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>50.88333, 24.03333</t>
+          <t>-16.59056, -39.09583</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>49</v>
+        <v>7171.5</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -7259,7 +7235,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Q934815</t>
+          <t>Q938536</t>
         </is>
       </c>
       <c r="J81" t="inlineStr"/>
@@ -7267,38 +7243,38 @@
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007559990305171</t>
+          <t>https://www.nli.org.il/he/authorities/987007567226805171</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>בכר (אלג'יריה)</t>
+          <t>מאיקאמר (גרמניה)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Béchar (Algeria)</t>
+          <t>Maikammer (Germany)</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>987007567374905171</t>
+          <t>987007566958205171</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>31.81499, -1.87823</t>
+          <t>48.30000, 8.13333</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>31.63333, -2.20000</t>
+          <t>49.30471, 8.12527</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>36.5</v>
+        <v>111.7</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -7307,55 +7283,51 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>Q638704</t>
-        </is>
-      </c>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr">
         <is>
-          <t>6296382</t>
+          <t>6555203</t>
         </is>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007567374905171</t>
+          <t>https://www.nli.org.il/he/authorities/987007566958205171</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ארביל (עיראק)</t>
+          <t>איים איוניים (יוון)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Erbil (Iraq)</t>
+          <t>Ionian Islands (Greece)</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>987007564435605171</t>
+          <t>987007560546705171</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>36.36908, 44.55924</t>
+          <t>38.50000, 20.50000</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>36.19111, 44.00944</t>
+          <t>37.80000, 20.70000</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>53.1</v>
+        <v>79.8</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -7369,152 +7341,160 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Q132754</t>
+          <t>Q170295</t>
         </is>
       </c>
       <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>6697805</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007564435605171</t>
+          <t>https://www.nli.org.il/he/authorities/987007560546705171</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>חנטשין (מחוז שוויינטוקז'יסקיה, פולין)</t>
+          <t>סמרנג (אינדונזיה)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Chęciny (Województwo Świętokrzyskie, Poland)</t>
+          <t>Semarang (Indonesia)</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>987007564539905171</t>
+          <t>987007564323305171</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>50.81128, 20.46710</t>
+          <t>-3.78945, 102.29781</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>51.86833, 21.74556</t>
+          <t>-6.99000, 110.42250</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>147.3</v>
+        <v>967.2</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
+          <t>Kima is bound to a same-named place elsewhere — a link error, not a move</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Q928099</t>
+          <t>Q13544450</t>
         </is>
       </c>
       <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>1627896</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007564539905171</t>
+          <t>https://www.nli.org.il/he/authorities/987007564323305171</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>טרנקוזו (ברזיל)</t>
+          <t>נג'ומבה (טנזניה)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Trancoso (Brazil)</t>
+          <t>Njombe (Tanzania)</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>987007567226805171</t>
+          <t>987007562661405171</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>40.78330, -7.35000</t>
+          <t>-90.33333, 34.76667</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>-16.59056, -39.09583</t>
+          <t>-9.41667, 34.75000</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>7171.5</v>
+        <v>8997.5</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
+          <t>Kima is bound to a same-named place elsewhere — a link error, not a move</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>Q938536</t>
-        </is>
-      </c>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>8469241</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007567226805171</t>
+          <t>https://www.nli.org.il/he/authorities/987007562661405171</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>מאיקאמר (גרמניה)</t>
+          <t>ג'דידה (מרוקו)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Maikammer (Germany)</t>
+          <t>Jadīdah (Morocco)</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>987007566958205171</t>
+          <t>987007561813405171</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>48.30000, 8.13333</t>
+          <t>33.53106, -7.67457</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>49.30471, 8.12527</t>
+          <t>33.23420, -8.52280</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>111.7</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -7523,51 +7503,55 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Q219583</t>
+        </is>
+      </c>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr">
         <is>
-          <t>6555203</t>
+          <t>105510</t>
         </is>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007566958205171</t>
+          <t>https://www.nli.org.il/he/authorities/987007561813405171</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>איים איוניים (יוון)</t>
+          <t>אנז'ו (צרפת)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Ionian Islands (Greece)</t>
+          <t>Anjou (France)</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>987007560546705171</t>
+          <t>987007564668505171</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>38.50000, 20.50000</t>
+          <t>45.35000, 4.88333</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>37.80000, 20.70000</t>
+          <t>47.46667, -0.55000</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>79.8</v>
+        <v>478.3</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -7581,50 +7565,46 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Q170295</t>
+          <t>Q107426</t>
         </is>
       </c>
       <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>6697805</t>
-        </is>
-      </c>
+      <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007560546705171</t>
+          <t>https://www.nli.org.il/he/authorities/987007564668505171</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>סמרנג (אינדונזיה)</t>
+          <t>מניקה (מוזמביק : פרובינציה)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Semarang (Indonesia)</t>
+          <t>Manica (Mozambique : Province)</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>987007564323305171</t>
+          <t>987007567544605171</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>-3.78945, 102.29781</t>
+          <t>-18.93444, 32.87556</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>-6.99000, 110.42250</t>
+          <t>-19.50000, 33.25000</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>967.2</v>
+        <v>74.2</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -7638,50 +7618,46 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Q13544450</t>
+          <t>Q383170</t>
         </is>
       </c>
       <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>1627896</t>
-        </is>
-      </c>
+      <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007564323305171</t>
+          <t>https://www.nli.org.il/he/authorities/987007567544605171</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>נג'ומבה (טנזניה)</t>
+          <t>בארי (סומליה)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Njombe (Tanzania)</t>
+          <t>Bari (Somalia)</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>987007562661405171</t>
+          <t>987007567541105171</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>-90.33333, 34.76667</t>
+          <t>26.63000, 77.62000</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>-9.41667, 34.75000</t>
+          <t>10.83333, 50.18333</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>8997.5</v>
+        <v>3368.2</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -7693,48 +7669,48 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Q707848</t>
+        </is>
+      </c>
       <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>8469241</t>
-        </is>
-      </c>
+      <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007562661405171</t>
+          <t>https://www.nli.org.il/he/authorities/987007567541105171</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ג'דידה (מרוקו)</t>
+          <t>בריל (באדן-וירטמברג, גרמניה)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Jadīdah (Morocco)</t>
+          <t>Brühl (Baden-Württemberg, Germany)</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>987007561813405171</t>
+          <t>987007561828205171</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>33.53106, -7.67457</t>
+          <t>49.40000, 8.53333</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>33.23420, -8.52280</t>
+          <t>50.36210, 9.64677</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>85.40000000000001</v>
+        <v>133.4</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -7748,64 +7724,60 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Q219583</t>
+          <t>Q996914</t>
         </is>
       </c>
       <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>105510</t>
-        </is>
-      </c>
+      <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007561813405171</t>
+          <t>https://www.nli.org.il/he/authorities/987007561828205171</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>אנז'ו (צרפת)</t>
+          <t>גנגס (צרפת)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Anjou (France)</t>
+          <t>Ganges (France)</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>987007564668505171</t>
+          <t>987007567552405171</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>45.35000, 4.88333</t>
+          <t>22.08330, 90.83330</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>47.46667, -0.55000</t>
+          <t>43.93417, 3.70833</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>478.3</v>
+        <v>8104.2</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
+          <t>Kima is bound to a same-named place elsewhere — a link error, not a move</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Q107426</t>
+          <t>Q5089</t>
         </is>
       </c>
       <c r="J91" t="inlineStr"/>
@@ -7813,105 +7785,109 @@
       <c r="L91" t="inlineStr"/>
       <c r="M91" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007564668505171</t>
+          <t>https://www.nli.org.il/he/authorities/987007567552405171</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>מניקה (מוזמביק : פרובינציה)</t>
+          <t>חאסקובו (בולגריה)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Manica (Mozambique : Province)</t>
+          <t>Khaskovo (Bulgaria)</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>987007567544605171</t>
+          <t>987007561902705171</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>-18.93444, 32.87556</t>
+          <t>41.76302, 25.89925</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>-19.50000, 33.25000</t>
+          <t>41.93465, 25.55556</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>74.2</v>
+        <v>34.3</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Kima is bound to a same-named place elsewhere — a link error, not a move</t>
+          <t>Wikidata backs Kima's point; NLI's stands alone</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Q383170</t>
+          <t>Q186254</t>
         </is>
       </c>
       <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>730435</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007567544605171</t>
+          <t>https://www.nli.org.il/he/authorities/987007561902705171</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>בארי (סומליה)</t>
+          <t>האורה (הודו)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Bari (Somalia)</t>
+          <t>Hāora (India)</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>987007567541105171</t>
+          <t>987007564798905171</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>26.63000, 77.62000</t>
+          <t>22.62140, 88.30433</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>10.83333, 50.18333</t>
+          <t>23.38642, 87.51565</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>3368.2</v>
+        <v>117.3</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Kima is bound to a same-named place elsewhere — a link error, not a move</t>
+          <t>Wikidata backs Kima's point; NLI's stands alone</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Q707848</t>
+          <t>Q60817046</t>
         </is>
       </c>
       <c r="J93" t="inlineStr"/>
@@ -7919,38 +7895,38 @@
       <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007567541105171</t>
+          <t>https://www.nli.org.il/he/authorities/987007564798905171</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>בריל (באדן-וירטמברג, גרמניה)</t>
+          <t>קרוביה (פולין)</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Brühl (Baden-Württemberg, Germany)</t>
+          <t>Krobia (Leszno, Poland)</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>987007561828205171</t>
+          <t>987007567354305171</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>49.40000, 8.53333</t>
+          <t>51.84406, 16.57560</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>50.36210, 9.64677</t>
+          <t>51.77500, 16.98333</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>133.4</v>
+        <v>29.1</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -7959,12 +7935,12 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Q996914</t>
+          <t>Q556944</t>
         </is>
       </c>
       <c r="J94" t="inlineStr"/>
@@ -7972,52 +7948,52 @@
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007561828205171</t>
+          <t>https://www.nli.org.il/he/authorities/987007567354305171</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>גנגס (צרפת)</t>
+          <t>רדין (בלארוס)</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Ganges (France)</t>
+          <t>Radunʹ (Belarus)</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>987007567552405171</t>
+          <t>987007560358905171</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>22.08330, 90.83330</t>
+          <t>53.45410, 26.36187</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>43.93417, 3.70833</t>
+          <t>54.05306, 24.99778</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>8104.2</v>
+        <v>111.7</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Kima is bound to a same-named place elsewhere — a link error, not a move</t>
+          <t>Wikidata backs Kima's point; NLI's stands alone</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Q5089</t>
+          <t>Q2995176</t>
         </is>
       </c>
       <c r="J95" t="inlineStr"/>
@@ -8025,38 +8001,38 @@
       <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007567552405171</t>
+          <t>https://www.nli.org.il/he/authorities/987007560358905171</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>חאסקובו (בולגריה)</t>
+          <t>סלנגינסק (רוסיה)</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Khaskovo (Bulgaria)</t>
+          <t>Selenginsk (Russia)</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>987007561902705171</t>
+          <t>987007564660405171</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>41.76302, 25.89925</t>
+          <t>51.10000, 106.61667</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>41.93465, 25.55556</t>
+          <t>52.00639, 106.86472</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>34.3</v>
+        <v>102.2</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -8065,69 +8041,65 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>Q186254</t>
-        </is>
-      </c>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr">
         <is>
-          <t>730435</t>
+          <t>2017059</t>
         </is>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007561902705171</t>
+          <t>https://www.nli.org.il/he/authorities/987007564660405171</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>האורה (הודו)</t>
+          <t>אייזן (צ'ילה : פרובינציה)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Hāora (India)</t>
+          <t>Aisén (Chile : Province)</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>987007564798905171</t>
+          <t>987007564309205171</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>22.62140, 88.30433</t>
+          <t>-45.40000, -72.70000</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>23.38642, 87.51565</t>
+          <t>-44.91667, -73.58333</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>117.3</v>
+        <v>87.7</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
+          <t>Kima is bound to a same-named place elsewhere — a link error, not a move</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Q60817046</t>
+          <t>Q3651</t>
         </is>
       </c>
       <c r="J97" t="inlineStr"/>
@@ -8135,38 +8107,38 @@
       <c r="L97" t="inlineStr"/>
       <c r="M97" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007564798905171</t>
+          <t>https://www.nli.org.il/he/authorities/987007564309205171</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>קרוביה (פולין)</t>
+          <t>סרנאנו (איטליה)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Krobia (Leszno, Poland)</t>
+          <t>Sarnano (Italy)</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>987007567354305171</t>
+          <t>987007600144505171</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>51.84406, 16.57560</t>
+          <t>43.34529, 13.29807</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>51.77500, 16.98333</t>
+          <t>43.03475, 13.29818</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>29.1</v>
+        <v>34.5</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -8178,105 +8150,109 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>Q556944</t>
-        </is>
-      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>3167119</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007567354305171</t>
+          <t>https://www.nli.org.il/he/authorities/987007600144505171</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>רדין (בלארוס)</t>
+          <t>מונדזיוב (פולין)</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Radunʹ (Belarus)</t>
+          <t>Modrzejów (Poland)</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>987007560358905171</t>
+          <t>987007498936105171</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>53.45410, 26.36187</t>
+          <t>51.26670, 21.25000</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>54.05306, 24.99778</t>
+          <t>50.24110, 19.14970</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>111.7</v>
+        <v>186.6</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
+          <t>Kima is bound to a same-named place elsewhere — a link error, not a move</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Q2995176</t>
+          <t>Q767989</t>
         </is>
       </c>
       <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>3091543</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007560358905171</t>
+          <t>https://www.nli.org.il/he/authorities/987007498936105171</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>סלנגינסק (רוסיה)</t>
+          <t>אלפורד (סקוטלנד : פאריש)</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Selenginsk (Russia)</t>
+          <t>Alford (Scotland : Parish)</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>987007564660405171</t>
+          <t>987007480078105171</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>51.10000, 106.61667</t>
+          <t>53.26000, 0.18000</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>52.00639, 106.86472</t>
+          <t>57.22560, -2.73196</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>102.2</v>
+        <v>477.9</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
+          <t>Kima is bound to a same-named place elsewhere — a link error, not a move</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -8284,48 +8260,48 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr"/>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Q1876378</t>
+        </is>
+      </c>
       <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>2017059</t>
-        </is>
-      </c>
+      <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr"/>
       <c r="M100" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007564660405171</t>
+          <t>https://www.nli.org.il/he/authorities/987007480078105171</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>אייזן (צ'ילה : פרובינציה)</t>
+          <t>לטרון (ישראל)</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Aisén (Chile : Province)</t>
+          <t>Latrun (Israel)</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>987007564309205171</t>
+          <t>987007557401105171</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>-45.40000, -72.70000</t>
+          <t>33.19538, 35.41241</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>-44.91667, -73.58333</t>
+          <t>31.83556, 34.98028</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>87.7</v>
+        <v>156.5</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -8339,7 +8315,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Q3651</t>
+          <t>Q681554</t>
         </is>
       </c>
       <c r="J101" t="inlineStr"/>
@@ -8347,38 +8323,38 @@
       <c r="L101" t="inlineStr"/>
       <c r="M101" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007564309205171</t>
+          <t>https://www.nli.org.il/he/authorities/987007557401105171</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>סרנאנו (איטליה)</t>
+          <t>מערת עמוד (ישראל)</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Sarnano (Italy)</t>
+          <t>Ammud Cave (Israel)</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>987007600144505171</t>
+          <t>987007465731605171</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>43.34529, 13.29807</t>
+          <t>32.86667, 35.50000</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>43.03475, 13.29818</t>
+          <t>32.94588, 35.29633</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>34.5</v>
+        <v>21</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -8387,267 +8363,219 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Q481397</t>
+        </is>
+      </c>
       <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t>3167119</t>
-        </is>
-      </c>
+      <c r="K102" t="inlineStr"/>
       <c r="L102" t="inlineStr"/>
       <c r="M102" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007600144505171</t>
+          <t>https://www.nli.org.il/he/authorities/987007465731605171</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>מונדזיוב (פולין)</t>
+          <t>וינצנהיים (צרפת)</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Modrzejów (Poland)</t>
+          <t>Wintzenheim (France)</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>987007498936105171</t>
+          <t>987007484748005171</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>51.26670, 21.25000</t>
+          <t>48.62737, 7.27563</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>50.24110, 19.14970</t>
+          <t>48.07306, 7.29000</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>186.6</v>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>Kima is bound to a same-named place elsewhere — a link error, not a move</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>Q767989</t>
-        </is>
-      </c>
+        <v>61.6</v>
+      </c>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr">
         <is>
-          <t>3091543</t>
+          <t>2967337</t>
         </is>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007498936105171</t>
+          <t>https://www.nli.org.il/he/authorities/987007484748005171</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>אלפורד (סקוטלנד : פאריש)</t>
+          <t>טייבורן (לונדון, אנגליה)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Alford (Scotland : Parish)</t>
+          <t>Tyburn (London, England)</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>987007480078105171</t>
+          <t>987007469730505171</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>53.26000, 0.18000</t>
+          <t>52.51667, -1.81667</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>57.22560, -2.73196</t>
+          <t>51.51286, -0.16400</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>477.9</v>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>Kima is bound to a same-named place elsewhere — a link error, not a move</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>Q1876378</t>
-        </is>
-      </c>
+        <v>158.9</v>
+      </c>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007480078105171</t>
+          <t>https://www.nli.org.il/he/authorities/987007469730505171</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>לטרון (ישראל)</t>
+          <t>טרנטו (איטליה)</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Latrun (Israel)</t>
+          <t>Trento (Italy)</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>987007557401105171</t>
+          <t>987007550224705171</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>33.19538, 35.41241</t>
+          <t>46.20705, 11.49247</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>31.83556, 34.98028</t>
+          <t>46.06667, 11.11667</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>156.5</v>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>Kima is bound to a same-named place elsewhere — a link error, not a move</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>Q681554</t>
-        </is>
-      </c>
+        <v>32.9</v>
+      </c>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr"/>
       <c r="L105" t="inlineStr"/>
       <c r="M105" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007557401105171</t>
+          <t>https://www.nli.org.il/he/authorities/987007550224705171</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>מערת עמוד (ישראל)</t>
+          <t>פאקו שיאן (סין)</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Ammud Cave (Israel)</t>
+          <t>Faku Xian (China)</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>987007465731605171</t>
+          <t>987007540299505171</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>32.86667, 35.50000</t>
+          <t>42.38333, 123.20000</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>32.94588, 35.29633</t>
+          <t>42.50136, 123.40838</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>21</v>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>Q481397</t>
-        </is>
-      </c>
+        <v>21.6</v>
+      </c>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr"/>
       <c r="L106" t="inlineStr"/>
       <c r="M106" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007465731605171</t>
+          <t>https://www.nli.org.il/he/authorities/987007540299505171</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>וינצנהיים (צרפת)</t>
+          <t>מאלאבר (הודו)</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Wintzenheim (France)</t>
+          <t>Malabar (India)</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>987007484748005171</t>
+          <t>987007542867205171</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>48.62737, 7.27563</t>
+          <t>19.17908, 72.93791</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>48.07306, 7.29000</t>
+          <t>12.01670, 75.28330</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>61.6</v>
+        <v>835</v>
       </c>
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr"/>
@@ -8655,44 +8583,44 @@
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr">
         <is>
-          <t>2967337</t>
+          <t>1636747</t>
         </is>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007484748005171</t>
+          <t>https://www.nli.org.il/he/authorities/987007542867205171</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>טייבורן (לונדון, אנגליה)</t>
+          <t>לואן שי (סין)</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Tyburn (London, England)</t>
+          <t>Lu'an Shi (China)</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>987007469730505171</t>
+          <t>987007540547905171</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>52.51667, -1.81667</t>
+          <t>31.72028, 116.29917</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>51.51286, -0.16400</t>
+          <t>31.75425, 116.50778</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>158.9</v>
+        <v>20.1</v>
       </c>
       <c r="G108" t="inlineStr"/>
       <c r="H108" t="inlineStr"/>
@@ -8702,270 +8630,57 @@
       <c r="L108" t="inlineStr"/>
       <c r="M108" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007469730505171</t>
+          <t>https://www.nli.org.il/he/authorities/987007540547905171</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>אוטיניה (אוקראינה)</t>
+          <t>גורז' (רומניה)</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Otynii︠a︡ (Ukraine)</t>
+          <t>Gorj (Romania)</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>987007545173905171</t>
+          <t>987007548034005171</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>49.07778, 22.99528</t>
+          <t>45.91667, 23.41667</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>48.73389, 24.85694</t>
+          <t>45.04636, 23.28278</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>141.3</v>
+        <v>97.3</v>
       </c>
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>Q641272</t>
-        </is>
-      </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>676898</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007545173905171</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>טרנטו (איטליה)</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Trento (Italy)</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>987007550224705171</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>46.20705, 11.49247</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>46.06667, 11.11667</t>
-        </is>
-      </c>
-      <c r="F110" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="G110" t="inlineStr"/>
-      <c r="H110" t="inlineStr"/>
-      <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>https://www.nli.org.il/he/authorities/987007550224705171</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>פאקו שיאן (סין)</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Faku Xian (China)</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>987007540299505171</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>42.38333, 123.20000</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>42.50136, 123.40838</t>
-        </is>
-      </c>
-      <c r="F111" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="G111" t="inlineStr"/>
-      <c r="H111" t="inlineStr"/>
-      <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>https://www.nli.org.il/he/authorities/987007540299505171</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>מאלאבר (הודו)</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Malabar (India)</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>987007542867205171</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>19.17908, 72.93791</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>12.01670, 75.28330</t>
-        </is>
-      </c>
-      <c r="F112" t="n">
-        <v>835</v>
-      </c>
-      <c r="G112" t="inlineStr"/>
-      <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t>1636747</t>
-        </is>
-      </c>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>https://www.nli.org.il/he/authorities/987007542867205171</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>לואן שי (סין)</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Lu'an Shi (China)</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>987007540547905171</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>31.72028, 116.29917</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>31.75425, 116.50778</t>
-        </is>
-      </c>
-      <c r="F113" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="G113" t="inlineStr"/>
-      <c r="H113" t="inlineStr"/>
-      <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>https://www.nli.org.il/he/authorities/987007540547905171</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>גורז' (רומניה)</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Gorj (Romania)</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>987007548034005171</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>45.91667, 23.41667</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>45.04636, 23.28278</t>
-        </is>
-      </c>
-      <c r="F114" t="n">
-        <v>97.3</v>
-      </c>
-      <c r="G114" t="inlineStr"/>
-      <c r="H114" t="inlineStr"/>
-      <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t>676898</t>
-        </is>
-      </c>
-      <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
           <t>https://www.nli.org.il/he/authorities/987007548034005171</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M114"/>
+  <autoFilter ref="A1:M109"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9048,7 +8763,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -9059,8 +8774,9 @@
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="52" customWidth="1" min="9" max="9"/>
-    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="52" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9081,35 +8797,40 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
+          <t>סוג הפנייה</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
           <t>המזהה שברשומה</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>המזהה הנכון</t>
-        </is>
-      </c>
       <c r="F1" s="2" t="inlineStr">
         <is>
+          <t>המזהה הנכון / המוצע</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
           <t>נקודת NLI</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>נקודת כימה</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>מרחק (ק״מ)</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>הערת הסוקר</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>קישור לרשומה</t>
         </is>
@@ -9118,97 +8839,413 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ורז'ם גרנדה (ברזיל)</t>
+          <t>לוחביצה (אוקראינה)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Vargem Grande (Brazil)</t>
+          <t>Lokhvyt︠s︡i︠a︡ (Ukraine)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>987007564873205171</t>
+          <t>987007562429505171</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Q22014977</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
+          <t>מזהה שגוי</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Q12118513</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-8.83333, -42.50000</t>
+          <t>Q269512</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-21.90139, -43.18167</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>1454.9</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>-3.54306, -43.91583 הן הקואורדינטות הנכון (ראו ויקידאטה)</t>
-        </is>
+          <t>50.36667, 33.26667</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>50.36105, 33.26517</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>0.6</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007564873205171</t>
+          <t>בעיה בשם הערבי</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007562429505171</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>אוקיאניה</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Oceania</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>987007543674705171</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>מזהה שגוי</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Q538</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Q55643</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-21.00000, 166.00000</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-18.51020, 139.36710</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>2797.7</v>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007543674705171</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>אטרס-ברג (גרמניה)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Etters-Berg (Germany)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>987007561549805171</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>מזהה שגוי</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Q651583</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Q31547753</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>51.03333, 11.27972</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>51.86667, 10.58333</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>אלה הם שני מקומות שונים: העיר וההר. אם הכוונה לעיר, הויקידאטה הוא Q651583 והשם: הויקידאטה והקואורדינטות הנוכחיות ב-nli הן לא של etters-berg אלא של ettersburg הישוב. אם הכוונה היא להר, ממליצה לשנות את השם לאטרס-ברג (גרמניה: הר) והויקידאטה הוא  Q31547753</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007561549805171</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>נהר רריטן (ניו ג'רזי)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Raritan River (N.J.)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>987007546333605171</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>מזהה שגוי</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Q34709250</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Q749287</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>40.49722, -74.26444</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>40.62910, -74.88970</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007546333605171</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>באחו סיגורה (ספרד)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Bajo Segura (Spain)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>987007284646705171</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>מזהה מוצע</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Q972305</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>38.08333, 0.86667</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>38.06693, -0.84042</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>149.4</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007284646705171</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>גרינוולד (פולין)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Grunwald (Poland)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>987007564769205171</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>מזהה שגוי</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Q220090</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Q1025864</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>48.04831, 11.53169</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>53.48583, 20.09194</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>852.1</v>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007564769205171</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>ראס אל מא (אלג'יריה)</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Râs el Ma (Algeria)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>987011433524905171</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>מזהה שגוי</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
         <is>
           <t>Q1004716</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Q22928906</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>35.14069, -2.42455</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>36.11846, 5.52999</t>
         </is>
       </c>
-      <c r="H3" t="n">
+      <c r="I8" t="n">
         <v>726.9</v>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
         <is>
           <t>https://www.nli.org.il/he/authorities/987011433524905171</t>
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>אוטיניה (אוקראינה)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Otynii︠a︡ (Ukraine)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>987007545173905171</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>מזהה מוצע</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Q641272</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>49.07778, 22.99528</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>48.73389, 24.85694</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>141.3</v>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007545173905171</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J3"/>
+  <autoFilter ref="A1:K9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9556,7 +9593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -9608,104 +9645,67 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>לוחביצה (אוקראינה)</t>
+          <t>רנידוס (טורקיה : עיר קדומה)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Lokhvyt︠s︡i︠a︡ (Ukraine)</t>
+          <t>Cnidus (Turkey : Extinct city)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>987007562429505171</t>
+          <t>987007284075505171</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>בעיה בשם הערבי</t>
+          <t>הרמיזות כוללות את הסוגריים, שלא כבדרך כלל.  כמו כן, רנידוס נראה לי כטעות, צ״ל קנידוס.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>50.36667, 33.26667</t>
+          <t>36.68583, 27.37500</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>50.36105, 33.26517</t>
+          <t>36.68583, 27.37500</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007562429505171</t>
+          <t>https://www.nli.org.il/he/authorities/987007284075505171</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>רנידוס (טורקיה : עיר קדומה)</t>
-        </is>
-      </c>
+      <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cnidus (Turkey : Extinct city)</t>
+          <t>North Huntingdon (Pa. : Township)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>987007284075505171</t>
+          <t>987007562247105171</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>הרמיזות כוללות את הסוגריים, שלא כבדרך כלל.  כמו כן, רנידוס נראה לי כטעות, צ״ל קנידוס.</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>36.68583, 27.37500</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>36.68583, 27.37500</t>
-        </is>
-      </c>
+          <t>הסוגר הסופי חסר בכותרת.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007284075505171</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>North Huntingdon (Pa. : Township)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>987007562247105171</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>הסוגר הסופי חסר בכותרת.</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
-        <is>
           <t>https://www.nli.org.il/he/authorities/987007562247105171</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G4"/>
+  <autoFilter ref="A1:G3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9889,27 +9889,27 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>מזהה ויקינתונים בשדה 024 מצביע על ישות שגויה</t>
+          <t>מזהה ויקינתונים בשדה 024</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>הרשומה מפנה בשדה 024 לישות ויקינתונים שאינה המקום שבכותרת — ישות בעלת שם דומה, או מקום אחר לגמרי. זו תקלה חמורה יותר מקואורדינטה שגויה, משום שהיא מתפשטת: כל מי שמסתמך על המזהה הזה כדי לקשר את הרשומה למקורות חיצוניים יורש את הטעות.</t>
+          <t>שני מצבים, ועמודת "סוג הפנייה" מבדילה ביניהם. &lt;b&gt;מזהה שגוי:&lt;/b&gt; הרשומה מפנה בשדה 024 לישות ויקינתונים שאינה המקום שבכותרת — ישות בעלת שם דומה, או מקום אחר לגמרי. זו תקלה חמורה יותר מקואורדינטה שגויה, משום שהיא מתפשטת: כל מי שמסתמך על המזהה הזה כדי לקשר את הרשומה למקורות חיצוניים יורש את הטעות. &lt;b&gt;מזהה מוצע:&lt;/b&gt; אין ברשומה 024 כלל, ואיתרנו את הישות המתאימה — הצעה, לא דיווח על שגיאה.</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>לתקן את המזהה בשדה 024. עמודת "המזהה הנכון" נושאת את הישות שלדעתנו הכותרת מתארת.</t>
+          <t>במקרים של מזהה שגוי — לתקן את שדה 024. במקרים של מזהה מוצע — לשקול להוסיף אותו. עמודת "המזהה הנכון / המוצע" נושאת את הישות שלדעתנו הכותרת מתארת.</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>לכל שורה הוצאנו את הישות שהמזהה מפנה אליה, את תווית השם שלה ואת הקואורדינטות שלה, והשווינו לכותרת הרשומה ולנקודה שבה. כשהתווית והנקודה שתיהן אינן מתאימות — המזהה שגוי.</t>
+          <t>לכל שורה הוצאנו את הישות שהמזהה מפנה אליה, את תווית השם שלה ואת הקואורדינטות שלה, והשווינו לכותרת הרשומה ולנקודה שבה. כשהתווית והנקודה שתיהן אינן מתאימות — המזהה שגוי. חלק מן השורות כאן התגלו תוך כדי בדיקת הקואורדינטות, ולכן יש בהן גם אי־התאמה במיקום; היא מופיעה בעמודת המרחק.</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>עמודות "תווית הישות" ו"נקודת הישות" מראות מה המזהה הקיים מתאר.</t>
+          <t>עמודת "סוג הפנייה" אומרת אם מדובר בתיקון או בהצעה, ועמודת "המזהה שברשומה" מראה מה קיים היום.</t>
         </is>
       </c>
     </row>

--- a/docs/nli-report-20260922.xlsx
+++ b/docs/nli-report-20260922.xlsx
@@ -2835,8 +2835,8 @@
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
+    <col hidden="1" width="34" customWidth="1" min="7" max="7"/>
+    <col hidden="1" width="16" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
@@ -6345,11 +6345,11 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>-21.90139, -43.18167</t>
+          <t>-3.54306, -43.91583</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>1454.9</v>
+        <v>608.7</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -9835,7 +9835,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>עמודת "ביטחון" היא ביטחון הסיווג האוטומטי; כל השורות כאן עברו גם אישור ידני.</t>
+          <t>עמודת "הנקודה שלדעתנו נכונה" היא הנקודה שכימה מחזיקה, אלא אם הסוקר רשם נקודה משלו — במקרים שבהם גם נקודת כימה שגויה. עמודת "מרחק" היא המרחק בין נקודת הרשומה לנקודה הזאת.</t>
         </is>
       </c>
     </row>

--- a/docs/nli-report-20260922.xlsx
+++ b/docs/nli-report-20260922.xlsx
@@ -12,17 +12,23 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="קואורדינטות שגויות" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="034 פגום" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="מזהה ויקינתונים" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="כפילות ברשומות" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="בודדות" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="הסברים" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="כותרת לשני מקומות" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="איות הכותרת" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="זהות הכותרת" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="כפילות ברשומות" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="בודדות" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="הסברים" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'אפס שנשמט'!$A$1:$J$45</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'קואורדינטות שגויות'!$A$1:$M$109</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'034 פגום'!$A$1:$E$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'מזהה ויקינתונים'!$A$1:$K$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'כפילות ברשומות'!$A$1:$J$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'בודדות'!$A$1:$G$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'כותרת לשני מקומות'!$A$1:$M$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'איות הכותרת'!$A$1:$G$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'זהות הכותרת'!$A$1:$G$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'כפילות ברשומות'!$A$1:$J$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'בודדות'!$A$1:$G$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -448,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A18"/>
+  <dimension ref="A1:A21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="95" customWidth="1" min="1" max="1"/>
@@ -474,7 +480,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>סך השורות: 169</t>
+          <t>סך השורות: 183</t>
         </is>
       </c>
     </row>
@@ -536,31 +542,531 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">    כפילות ברשומות — 6 שורות — שתי רשומות רשות לאותו מקום</t>
+          <t xml:space="preserve">    כותרת לשני מקומות — 8 שורות — כותרת עברית אחת לשני מקומות</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">    בודדות — 2 שורות — תקלות בודדות</t>
+          <t xml:space="preserve">    איות הכותרת — 3 שורות — שגיאה באיות הכותרת העברית</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    זהות הכותרת — 4 שורות — הכותרת העברית שייכת לרשומה אחרת</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>כל שורה עברה סקירה ידנית. עמודת "הערת הסוקר" נושאת את הממצא</t>
+          <t xml:space="preserve">    כפילות ברשומות — 6 שורות — שתי רשומות רשות לאותו מקום</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t xml:space="preserve">    בודדות — 1 שורות — תקלות בודדות</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>כל שורה עברה סקירה ידנית. עמודת "הערת הסוקר" נושאת את הממצא</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>כפי שנרשם בעת הסקירה.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>כותרת עברית</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>כותרת לטינית</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>מזהה NLI</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>הערת הסוקר</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>נקודת NLI</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>נקודת כימה</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>קישור לרשומה</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>North Huntingdon (Pa. : Township)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>987007562247105171</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>הסוגר הסופי חסר בכותרת.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007562247105171</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G2"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="62" customWidth="1" min="4" max="4"/>
+    <col width="62" customWidth="1" min="5" max="5"/>
+    <col width="62" customWidth="1" min="6" max="6"/>
+    <col width="62" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>מפתח (לא לערוך)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>שם הלשונית</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>כותרת</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>מה קרה</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>מה מבוקש מן הספרייה</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>איך נמצא</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>העדות בטבלה</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>dropped-zero</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>אפס שנשמט</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>אפס מוביל שנשמט משדה 034</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>בשדה 034 של הרשומות האלה אחד מתתי־השדות של הקואורדינטות קצר בספרה אחת: האפס המוביל נשמט בכתיבה. הערך &lt;code&gt;E0120000&lt;/code&gt; נכתב &lt;code&gt;E120000&lt;/code&gt;, והמנתח קורא אותו כ־12° במקום 1.2°, או מזיז את הנקודה בעשרות ומאות קילומטרים. התיבה שנוצרת אינה מקיפה את המקום, ומרכזה נופל במקום אחר לגמרי — לעתים בים, לעתים במדינה שכנה.</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>לתקן את ערכי 034 לפי העמודה "הערך המתוקן". זה תיקון מכני: הערך הנכון נגזר מן הערך הקיים בהוספת האפס החסר, ואינו דורש הכרעה עורכית באף אחד מן המקרים.</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>הגלאי יושב ב־&lt;code&gt;app/classify_moves.py&lt;/code&gt; ומזהה את התקלה לפי אורך תת־השדה ביחס לצורות התקינות של MARC 034. אחרי התיקון מרכז התיבה חוזר לשבת על המקום, ובבדיקה שלנו הוא חוזר להתלכד עם הנקודה שכימה מחזיקה.</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>כל שורה: הערך הפגום כפי שהוא ברשומה, הערך המתוקן, והמרחק שהתיקון סוגר.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>nli-coords</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>קואורדינטות שגויות</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>הקואורדינטות ברשומה מצביעות על מקום אחר</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>בשורות האלה שדה 034 תקין מבחינה צורנית, אבל הנקודה שהוא מתאר אינה המקום שבכותרת. בחלק מן המקרים נבחר הומונים שגוי — יישוב בעל אותו שם ביבשת אחרת (Phoenicia שבניו־יורק במקום פיניקיה שבלבנון; Linden שבניו־ג׳רזי במקום לינדן שבגיאנה). באחרים הנקודה פשוט שגויה, בלי שנוכל להצביע על מקור הטעות.</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>לבדוק את הקואורדינטות בכל שורה מול הכותרת, ולתקן את 034. העמודות "נקודת ויקינתונים" ו"מרחק" מראות מה לדעתנו הנקודה הנכונה ועד כמה הרשומה רחוקה ממנה.</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>ההשוואה נעשתה בין שלוש נקודות: זו שברשומת NLI, זו שכימה מחזיקה, וזו של ישות הוויקינתונים שהרשומה עצמה מפנה אליה בשדה 024. כשכימה וויקינתונים מסכימות זו עם זו ונקודת NLI לבדה — ייחסנו את הטעות לרשומה. הסיווג האוטומטי עבר אחר כך סקירה ידנית, שורה שורה.</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>עמודת "הנקודה שלדעתנו נכונה" היא הנקודה שכימה מחזיקה, אלא אם הסוקר רשם נקודה משלו — במקרים שבהם גם נקודת כימה שגויה. עמודת "מרחק" היא המרחק בין נקודת הרשומה לנקודה הזאת.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>malformed-034</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>034 פגום</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>שדה 034 שאינו ניתן לניתוח</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>שדה 034 שאינו עומד באף אחת מן הצורות שMARC מתיר — לא מעלות עשרוניות ולא &lt;code&gt;hdddmmss&lt;/code&gt; — ולכן אין ממנו קואורדינטה כלל. הרשומה נראית כאילו יש בה מיקום, אבל בפועל אין.</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>לתקן את הערכים לצורה תקינה. הדוח המלא של התקלה הזאת נמסר בנפרד (957 רשומות, &lt;code&gt;nli-malformed-coordinates-report_20260822.csv&lt;/code&gt;) — כאן מופיעות רק השורות שעלו גם בסקירה הזאת.</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>מנתח הקואורדינטות שלנו מקבל את שתי הצורות התקינות ומרפד DMS קצר. מה שנשאר כאן לא נותח גם אחרי הריפוד.</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>ראו את הדוח הנפרד לפירוט מלא לפי סוג התקלה.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>wikidata-id</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>מזהה ויקינתונים</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>מזהה ויקינתונים בשדה 024</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>שני מצבים, ועמודת "סוג הפנייה" מבדילה ביניהם. &lt;b&gt;מזהה שגוי:&lt;/b&gt; הרשומה מפנה בשדה 024 לישות ויקינתונים שאינה המקום שבכותרת — ישות בעלת שם דומה, או מקום אחר לגמרי. זו תקלה חמורה יותר מקואורדינטה שגויה, משום שהיא מתפשטת: כל מי שמסתמך על המזהה הזה כדי לקשר את הרשומה למקורות חיצוניים יורש את הטעות. &lt;b&gt;מזהה מוצע:&lt;/b&gt; אין ברשומה 024 כלל, ואיתרנו את הישות המתאימה — הצעה, לא דיווח על שגיאה.</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>במקרים של מזהה שגוי — לתקן את שדה 024. במקרים של מזהה מוצע — לשקול להוסיף אותו. עמודת "המזהה הנכון / המוצע" נושאת את הישות שלדעתנו הכותרת מתארת.</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>לכל שורה הוצאנו את הישות שהמזהה מפנה אליה, את תווית השם שלה ואת הקואורדינטות שלה, והשווינו לכותרת הרשומה ולנקודה שבה. כשהתווית והנקודה שתיהן אינן מתאימות — המזהה שגוי. חלק מן השורות כאן התגלו תוך כדי בדיקת הקואורדינטות, ולכן יש בהן גם אי־התאמה במיקום; היא מופיעה בעמודת המרחק.</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>עמודת "סוג הפנייה" אומרת אם מדובר בתיקון או בהצעה, ועמודת "המזהה שברשומה" מראה מה קיים היום.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>heb-homonym</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>כותרת לשני מקומות</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>כותרת עברית אחת לשני מקומות</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>שתי רשומות רשות נפרדות — שני מקומות ממשיים ושונים — נושאות בדיוק את אותה כותרת בעברית, אף שהשם הלטיני מבדיל ביניהן. התעתיק לעברית מאבד את ההבחנה: Ehningen ו־Eningen unter Achalm נעשים שניהם "אנינגן (גרמניה)", Lüben ו־Lübben שניהם "לובן (גרמניה)". התוצאה היא שאי אפשר להפנות לאחת מהן בעברית בלי להפנות גם לשנייה.</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>להוסיף מבחין לכותרת העברית של כל אחד מן הצדדים. העמודות "הצעה לרשומה הנכנסת" ו"הצעה לרשומה הקיימת" נושאות הצעה קונקרטית לכל צד. ההצעות המסומנות "טיוטה" הן הצעות שלנו ולא הכרעה — הן נסמכות על החלוקה המנהלית בוויקינתונים, ואנו מבקשים את דעתכם עליהן.</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>המקרים אותרו בהשוואת הכותרות העבריות בין הרשומה הנכנסת ובין הרשומה שכבר מחזיקה את אותה כותרת. לכל זוג בדקנו את השם הלטיני, את מזהה הוויקינתונים ואת הקואורדינטות, כדי לוודא שמדובר בשני מקומות ולא בכפילות. שמות המחוזות בהצעות לקוחים מתוויות ויקינתונים בעברית, לא מתעתיק שלנו.</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>עמודת "מרחק" מראה כמה רחוקים המקומות זה מזה — עדות לכך שאינם אותו מקום. עמודת "נימוק ההצעה" מסבירה על מה נשענת כל טיוטה.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>heb-spelling</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>איות הכותרת</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>שגיאה באיות הכותרת העברית</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>כאן אין עמימות ואין שני מקומות — פשוט האיות העברי של הכותרת שגוי, או שהכותרת מעלה שאלה של זהות. אלה ממצאים שעלו אגב בדיקות אחרות ונרשמו במהלך הסקירה.</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>לתקן את האיות לפי העמודה "האיות המוצע", או — במקרה של שטרסבורג — להכריע בשאלה שבעמודת ההסבר.</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>כל מקרה נבדק מול השם הלטיני ברשומה ומול ויקינתונים. אלה מקרים בודדים שנרשמו ידנית, לא תוצר של סיווג אוטומטי.</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>עמודת "האיות ברשומה" מול "האיות המוצע", וההסבר שלצדן.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>heb-identity</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>זהות הכותרת</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>הכותרת העברית שייכת לרשומה אחרת</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>מקרים שבהם הבעיה אינה באיות אלא בשיוך: כותרת עברית שיושבת על הרשומה הלא נכונה, או שתי רשומות שהן למעשה מקום אחד ויש לאחדן. אלה אינם מקרים שדורשים מבחין — הם דורשים הכרעה מה הרשומה מתארת.</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>לבדוק כל מקרה לגופו לפי ההערה שלצדו: לאחד את הרשומות, או להעביר את הכותרת העברית לרשומה שאליה היא שייכת.</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>אותרו במהלך סקירת הכפילויות ואומתו מול MARC מ־Alma OAI.</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>עמודת "הערת הסוקר" נושאת את הממצא המלא לכל שורה.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>duplicate-records</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>כפילות ברשומות</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>שתי רשומות רשות לאותו מקום</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>שתי רשומות רשות נפרדות ב־NLI מתארות מקום אחד. בחלק מן המקרים העדות היא מזהה ויקינתונים זהה בשתיהן; באחרים אחת הכותרות היא שם היסטורי של האחרת (טולבוחין ודובריץ׳). זו אינה שאלה של איות עברי אלא של זהות הרשומה: הרשות כפולה.</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>לבדוק את הזוגות ולמזג את הרשומות, או להסביר מה מבדיל ביניהן אם ההפרדה מכוונת.</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>הזוגות אותרו לפי מזהה ויקינתונים משותף ולפי הודעות הכפילות של ההרצה השבועית, ואומתו אחת אחת מול MARC מ־Alma OAI.</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>כל שורה נושאת את שני המזהים ואת שתי הכותרות.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>בודדות</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>תקלות בודדות</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>מקרים שאינם מצטרפים לתבנית — תקלה בשם הערבי, סוגר שלא נסגר בכותרת, סוגריים שנכנסו להפניה. כל שורה עומדת בזכות עצמה, וההערה שלצדה אומרת מה נמצא.</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>לקרוא את ההערה בכל שורה ולתקן בהתאם.</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>אלה מקרים שעלו במהלך סקירת קטגוריות אחרות. חלקם הוכרעו בהרצה מוקדמת יותר, והנתונים שלהם נשלפו מחדש מ־Alma OAI לצורך הדוח הזה.</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>עמודת "הערה" היא הממצא עצמו.</t>
         </is>
       </c>
     </row>
@@ -9256,6 +9762,880 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="52" customWidth="1" min="12" max="12"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>הכותרת העברית המשותפת</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>מעמד ההצעה</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>הרשומה הנכנסת (לטינית)</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>מזהה NLI</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>הצעה לרשומה הנכנסת</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>הרשומה הקיימת (לטינית)</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>מזהה הרשומה הקיימת</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>הצעה לרשומה הקיימת</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>מרחק (ק״מ)</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>נימוק ההצעה</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>לבדיקה לפני שליחה</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>הערת הסוקר</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>קישור לרשומה</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>הוכשטטן (גרמניה)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>טיוטה</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Hochstätten (Germany)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>987011060395805171</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>הוכשטטן (מחוז באד קרויצנאך, גרמניה)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Hochstetten (Germany)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>987007467698905171</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>הוכשטטן (גרמניה)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>שתי רשומות שונות: Hochstätten שבמחוז באד קרויצנאך, ו־Hochstetten באיות אחר. ההצעה מוסיפה את המחוז לרשומה הנכנסת; יש לאשר מהי הרשומה השנייה לפני שמציעים לה מבחין.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987011060395805171</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>קאבה (הונגריה)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Kaba (Hungary)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>987007562214205171</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>קאבה (היידו-ביהר, הונגריה)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Káva (Hungary)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>987007373278105171</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>קאבה (פשט, הונגריה)</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>127.4</v>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007562214205171</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>אנינגן (גרמניה)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>טיוטה</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ehningen (Germany)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>987007494092005171</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>אנינגן (מחוז בבלינגן, גרמניה)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Eningen unter Achalm (Germany)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>987007557723505171</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>אנינגן אונטר אכלם (מחוז רויטלינגן, גרמניה)</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>שני יישובים שונים במרחק 31 ק״מ: Ehningen שבמחוז בבלינגן (Q314758) ו־Eningen unter Achalm שבמחוז רויטלינגן (Q81423). שמות המחוזות לקוחים מתוויות ויקינתונים בעברית.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007494092005171</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>צ'רנייב (אוקראינה)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>טיוטה</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Cherniïv (Ukraine)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>987007545176905171</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>צ'רנייב (מחוז איוונו-פרנקיבסק, אוקראינה)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Chernihiv (Ukraine)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>987007566754005171</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>צ'רניהיב (אוקראינה)</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>552.8</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>כאן לא די במבחין: המרחק 553 ק״מ, והרשומה השנייה היא צ׳רניהיב — בירת המחוז (Q157053), שהתעתיק העברי המקובל לה בוויקינתונים הוא "צ׳רניהיב" ולא "צ׳רנייב". כלומר אחת הכותרות שגויה ולא רק עמומה.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007545176905171</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>לובן (גרמניה)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>טיוטה</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Lüben (Germany)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>987007494367505171</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>לובין (מחוז דולנוסלונסקיה, פולין)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Lübben (Germany)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>987007473617305171</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>לובן (מחוז דאמה-שפרוואלד, גרמניה)</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>170</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>לפי הערת הסוקר, הרשומה הנכנסת היא Lubin שבפולין — השם העכשווי — ו־Lüben/Lueben הם וריאנטים היסטוריים שלה. הרשומה השנייה היא Lübben שבברנדנבורג (Q584815). שני מקומות שונים ב־170 ק״מ.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>צריך להיות Lubin (Dolnośląskie, Poland)  - השם העכשווי. luben כמו גם Lueben צריכים להיות וריאנטים.</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007494367505171</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>מריון (פנסילבניה)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Merion (Pa.)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>987007559599105171</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>מריון סטיישן (פנסילבניה)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>מריון (פנסילבניה)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>לצורך דיסאמביגואציה של השם בעברית. לחלופין, אפשר להוסיף מחוזות (מונטגומרי, פרנקלין), אם כי מריון סטיישן הוא השם המוכר יותר.</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007559599105171</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>פוליני (צרפת)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Pulligny (France)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>987010489292905171</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>פוליני (מחוז יורה, צרפת)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>פוליני (מחוז מרת ומוזל, צרפת)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>לבדיקה: הרשומה הנכנסת היא Pulligny, ולפי ויקינתונים (Q1099419) היא במחוז מרת ומוזל — ואילו ההצעה מייחסת אותה ליורה. ייתכן ששני הצדדים הוחלפו. יש לאשר לפני שליחה.</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987010489292905171</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>אופנהיים (גרמניה)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Uffenheim (Germany)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>987011252608705171</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>אופנהיים (בוואריה, גרמניה)</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>אופנהיים (ריינלנד-פפאלץ, גרמניה)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987011252608705171</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:M9"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>כותרת עברית</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>כותרת לטינית</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>מזהה NLI</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>האיות ברשומה</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>האיות המוצע</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>הסבר</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>קישור לרשומה</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>שטרסבורג (גרמניה)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Strassburg (Germany)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>987007552593705171</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>שטרסבורג (גרמניה)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>אין כאן שגיאת איות אלא שאלת זהות: יש שטרסבורג גרמנית (Q565624) השונה מזו הצרפתית של היום. האם יש צורך לשמר את הזהות הזו? אם כן, מוטב להוסיף 1871-1918 לכותרת הראשית.</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007552593705171</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>איגולשטדט (גרמניה)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ingolstadt (Germany)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>987007559626405171</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>אינגולשטדט (גרמניה)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>איגולשטדט (גרמניה)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>האיות העברי אינו תואם את Ingolstadt.</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007559626405171</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>רנידוס (טורקיה : עיר קדומה)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Cnidus (Turkey : Extinct city)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>987007284075505171</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>רנידוס (טורקיה : עיר קדומה)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>קנידוס (טורקיה : עיר קדומה)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Cnidus — התעתיק המקובל הוא בקו״ף. כמו כן הסוגר הסופי חסר בכותרת, והרמיזות כוללות את הסוגריים שלא כבדרך כלל.</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007284075505171</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G4"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>כותרת עברית</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>כותרת לטינית</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>מזהה NLI</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>הרשומה השנייה</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>כותרת הרשומה השנייה</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>הערת הסוקר</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>קישור לרשומה</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>פלאנס (ספרד)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Planes (Spain)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>987013405241405171</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>987007547821005171</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>פליינס, ספרד</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>כפילות ב־NLI: שתי רשומות חיות לאותו כפר — 987007547821005171 (Planes, Spain) ו־987013405241405171 (Planes (Spain)). שתיהן נושאות פלאנס (ספרד) בעברית. לדווח לספרייה. בכימה: לתקן את כותרת 76207 מ־'פליינס, ספרד' ל־'פלאנס (ספרד)' — פליינס היא שגיאת קריאה (Plains האנגלי במקום Planes הספרדי; ההשראה כנראה פליינס (ג'ורג'יה)/Plains (Ga.)). להפנות ל־987013405241405171 ולהוסיף Q1983306. פליינס אינה וריאנט לגיטימי — לכל היותר צורה מוקצית, לא שם חלופי.</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987013405241405171</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>אוסטרוויק (גרמניה)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Osterwieck (Germany)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>987007567653605171</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>987007540473305171</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>אוסטרוויק (גרמניה)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Osterwick הוא רובע ביישוב קטן, לא סביר שאליו הכוונה. הכיתוב הנכון הוא Osterwieck ולכן כדאי לאחד (בכימה) ולדווח כפילות ל-nli</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007567653605171</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>טרבזון (טורקיה)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ardeşen (Turkey)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>987007469750605171</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>987007562581305171</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>טרבזון (טורקיה)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>השם העברי של רשומה 987007469750605171</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007469750605171</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>המזרח הרחוק הרוסי (רוסיה)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Dalʹnevostochnyĭ federalʹnyĭ okrug (Russia)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>987007496754305171</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>987007560867505171</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>המזרח הרחוק הרוסי (רוסיה)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007496754305171</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G5"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -9585,409 +10965,4 @@
   <autoFilter ref="A1:J7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="52" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>כותרת עברית</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>כותרת לטינית</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>מזהה NLI</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>הערת הסוקר</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>נקודת NLI</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>נקודת כימה</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>קישור לרשומה</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>רנידוס (טורקיה : עיר קדומה)</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Cnidus (Turkey : Extinct city)</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>987007284075505171</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>הרמיזות כוללות את הסוגריים, שלא כבדרך כלל.  כמו כן, רנידוס נראה לי כטעות, צ״ל קנידוס.</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>36.68583, 27.37500</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>36.68583, 27.37500</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>https://www.nli.org.il/he/authorities/987007284075505171</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>North Huntingdon (Pa. : Township)</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>987007562247105171</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>הסוגר הסופי חסר בכותרת.</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>https://www.nli.org.il/he/authorities/987007562247105171</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:G3"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="62" customWidth="1" min="4" max="4"/>
-    <col width="62" customWidth="1" min="5" max="5"/>
-    <col width="62" customWidth="1" min="6" max="6"/>
-    <col width="62" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>מפתח (לא לערוך)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>שם הלשונית</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>כותרת</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>מה קרה</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>מה מבוקש מן הספרייה</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>איך נמצא</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>העדות בטבלה</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>dropped-zero</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>אפס שנשמט</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>אפס מוביל שנשמט משדה 034</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>בשדה 034 של הרשומות האלה אחד מתתי־השדות של הקואורדינטות קצר בספרה אחת: האפס המוביל נשמט בכתיבה. הערך &lt;code&gt;E0120000&lt;/code&gt; נכתב &lt;code&gt;E120000&lt;/code&gt;, והמנתח קורא אותו כ־12° במקום 1.2°, או מזיז את הנקודה בעשרות ומאות קילומטרים. התיבה שנוצרת אינה מקיפה את המקום, ומרכזה נופל במקום אחר לגמרי — לעתים בים, לעתים במדינה שכנה.</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>לתקן את ערכי 034 לפי העמודה "הערך המתוקן". זה תיקון מכני: הערך הנכון נגזר מן הערך הקיים בהוספת האפס החסר, ואינו דורש הכרעה עורכית באף אחד מן המקרים.</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>הגלאי יושב ב־&lt;code&gt;app/classify_moves.py&lt;/code&gt; ומזהה את התקלה לפי אורך תת־השדה ביחס לצורות התקינות של MARC 034. אחרי התיקון מרכז התיבה חוזר לשבת על המקום, ובבדיקה שלנו הוא חוזר להתלכד עם הנקודה שכימה מחזיקה.</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>כל שורה: הערך הפגום כפי שהוא ברשומה, הערך המתוקן, והמרחק שהתיקון סוגר.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>nli-coords</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>קואורדינטות שגויות</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>הקואורדינטות ברשומה מצביעות על מקום אחר</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>בשורות האלה שדה 034 תקין מבחינה צורנית, אבל הנקודה שהוא מתאר אינה המקום שבכותרת. בחלק מן המקרים נבחר הומונים שגוי — יישוב בעל אותו שם ביבשת אחרת (Phoenicia שבניו־יורק במקום פיניקיה שבלבנון; Linden שבניו־ג׳רזי במקום לינדן שבגיאנה). באחרים הנקודה פשוט שגויה, בלי שנוכל להצביע על מקור הטעות.</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>לבדוק את הקואורדינטות בכל שורה מול הכותרת, ולתקן את 034. העמודות "נקודת ויקינתונים" ו"מרחק" מראות מה לדעתנו הנקודה הנכונה ועד כמה הרשומה רחוקה ממנה.</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>ההשוואה נעשתה בין שלוש נקודות: זו שברשומת NLI, זו שכימה מחזיקה, וזו של ישות הוויקינתונים שהרשומה עצמה מפנה אליה בשדה 024. כשכימה וויקינתונים מסכימות זו עם זו ונקודת NLI לבדה — ייחסנו את הטעות לרשומה. הסיווג האוטומטי עבר אחר כך סקירה ידנית, שורה שורה.</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>עמודת "הנקודה שלדעתנו נכונה" היא הנקודה שכימה מחזיקה, אלא אם הסוקר רשם נקודה משלו — במקרים שבהם גם נקודת כימה שגויה. עמודת "מרחק" היא המרחק בין נקודת הרשומה לנקודה הזאת.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>malformed-034</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>034 פגום</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>שדה 034 שאינו ניתן לניתוח</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>שדה 034 שאינו עומד באף אחת מן הצורות שMARC מתיר — לא מעלות עשרוניות ולא &lt;code&gt;hdddmmss&lt;/code&gt; — ולכן אין ממנו קואורדינטה כלל. הרשומה נראית כאילו יש בה מיקום, אבל בפועל אין.</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>לתקן את הערכים לצורה תקינה. הדוח המלא של התקלה הזאת נמסר בנפרד (957 רשומות, &lt;code&gt;nli-malformed-coordinates-report_20260822.csv&lt;/code&gt;) — כאן מופיעות רק השורות שעלו גם בסקירה הזאת.</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>מנתח הקואורדינטות שלנו מקבל את שתי הצורות התקינות ומרפד DMS קצר. מה שנשאר כאן לא נותח גם אחרי הריפוד.</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>ראו את הדוח הנפרד לפירוט מלא לפי סוג התקלה.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>wikidata-id</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>מזהה ויקינתונים</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>מזהה ויקינתונים בשדה 024</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>שני מצבים, ועמודת "סוג הפנייה" מבדילה ביניהם. &lt;b&gt;מזהה שגוי:&lt;/b&gt; הרשומה מפנה בשדה 024 לישות ויקינתונים שאינה המקום שבכותרת — ישות בעלת שם דומה, או מקום אחר לגמרי. זו תקלה חמורה יותר מקואורדינטה שגויה, משום שהיא מתפשטת: כל מי שמסתמך על המזהה הזה כדי לקשר את הרשומה למקורות חיצוניים יורש את הטעות. &lt;b&gt;מזהה מוצע:&lt;/b&gt; אין ברשומה 024 כלל, ואיתרנו את הישות המתאימה — הצעה, לא דיווח על שגיאה.</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>במקרים של מזהה שגוי — לתקן את שדה 024. במקרים של מזהה מוצע — לשקול להוסיף אותו. עמודת "המזהה הנכון / המוצע" נושאת את הישות שלדעתנו הכותרת מתארת.</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>לכל שורה הוצאנו את הישות שהמזהה מפנה אליה, את תווית השם שלה ואת הקואורדינטות שלה, והשווינו לכותרת הרשומה ולנקודה שבה. כשהתווית והנקודה שתיהן אינן מתאימות — המזהה שגוי. חלק מן השורות כאן התגלו תוך כדי בדיקת הקואורדינטות, ולכן יש בהן גם אי־התאמה במיקום; היא מופיעה בעמודת המרחק.</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>עמודת "סוג הפנייה" אומרת אם מדובר בתיקון או בהצעה, ועמודת "המזהה שברשומה" מראה מה קיים היום.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>duplicate-records</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>כפילות ברשומות</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>שתי רשומות רשות לאותו מקום</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>שתי רשומות רשות נפרדות ב־NLI מתארות מקום אחד. בחלק מן המקרים העדות היא מזהה ויקינתונים זהה בשתיהן; באחרים אחת הכותרות היא שם היסטורי של האחרת (טולבוחין ודובריץ׳). זו אינה שאלה של איות עברי אלא של זהות הרשומה: הרשות כפולה.</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>לבדוק את הזוגות ולמזג את הרשומות, או להסביר מה מבדיל ביניהן אם ההפרדה מכוונת.</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>הזוגות אותרו לפי מזהה ויקינתונים משותף ולפי הודעות הכפילות של ההרצה השבועית, ואומתו אחת אחת מול MARC מ־Alma OAI.</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>כל שורה נושאת את שני המזהים ואת שתי הכותרות.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>בודדות</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>תקלות בודדות</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>מקרים שאינם מצטרפים לתבנית — תקלה בשם הערבי, סוגר שלא נסגר בכותרת, סוגריים שנכנסו להפניה. כל שורה עומדת בזכות עצמה, וההערה שלצדה אומרת מה נמצא.</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>לקרוא את ההערה בכל שורה ולתקן בהתאם.</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>אלה מקרים שעלו במהלך סקירת קטגוריות אחרות. חלקם הוכרעו בהרצה מוקדמת יותר, והנתונים שלהם נשלפו מחדש מ־Alma OAI לצורך הדוח הזה.</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>עמודת "הערה" היא הממצא עצמו.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>